--- a/output/rejected_schools.xlsx
+++ b/output/rejected_schools.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="522">
   <si>
     <t>rspo</t>
   </si>
@@ -1523,6 +1523,51 @@
   </si>
   <si>
     <t>SAMORZĄDOWA SZKOŁA PODSTAWOWA IM. JANUSZA KORCZAKA W PRZERADZU MAŁYM</t>
+  </si>
+  <si>
+    <t>SZKOŁA PODSTAWOWA IM." BOHATERÓW BITWY POD SARNOWĄ GÓRĄ 1920"W BĄDKOWIE</t>
+  </si>
+  <si>
+    <t>PUBLICZNA SZKOŁA PODSTAWOWA W CZĘSTONIEWIE IMIENIA ŚWIĘTEGO JANA PAWŁA II</t>
+  </si>
+  <si>
+    <t>NIEPUBLICZNA SZKOŁA PODSTAWOWA IM. KPT. Ż. W. DANUTY KOBYLIŃSKIEJ-WALAS W KOZIETUŁACH</t>
+  </si>
+  <si>
+    <t>SZKOŁA PODSTAWOWA IM PIOTRA WYSOCKIEGO W DROPIU</t>
+  </si>
+  <si>
+    <t>SZKOŁA PODSTAWOWA IM.MARII KONOPNICKIEJ W DĄBROWIE</t>
+  </si>
+  <si>
+    <t>PUBLICZNA SZKOŁA PODSTAWOWA IM. KARD. STEFANA WYSZYŃSKIEGO W WOLKOWYCH</t>
+  </si>
+  <si>
+    <t>CHRZEŚCIJAŃSKA NIEPUBLICZNA SZKOŁA PODSTAWOWA "KOMPAS"</t>
+  </si>
+  <si>
+    <t>SZKOŁA PODSTAWOWA IM. DOROTY GELLNER W POBYŁKOWIE DUŻYM</t>
+  </si>
+  <si>
+    <t>SZKOŁA PODSTAWOWA IM. KS. MACIEJA KAZIMIERZA SARBIEWSKIEGO W SARBIEWIE.</t>
+  </si>
+  <si>
+    <t>SZKOŁA PODSTAWOWA IM. WINCENTEGO WITOSA W JEŻEWIE</t>
+  </si>
+  <si>
+    <t>SZKOŁA PODSTAWOWA IM. J. KOCHANOWSKIEGO Z ODDZIAŁEM PRZEDSZKOLNYM</t>
+  </si>
+  <si>
+    <t>NIEPUBLICZNA SZKOŁA PODSTAWOWA WARSAW MONTESSORI SCHOOL</t>
+  </si>
+  <si>
+    <t>SPOŁECZNA SZKOŁA PODSTAWOWA FUNDACJI "ALTEREDU"</t>
+  </si>
+  <si>
+    <t>NIEPUBLICZNA SZKOŁA PODSTAWOWA IM. ELZBIETY MAKSYMOWICZ-MIŁOSZ</t>
+  </si>
+  <si>
+    <t>IZABELIŃSKA SZKOŁA MONTESSORI</t>
   </si>
   <si>
     <t>polski, matematyka, angielski</t>
@@ -1866,7 +1911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M775"/>
+  <dimension ref="A1:M873"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -1921,7 +1966,7 @@
         <v>2021</v>
       </c>
       <c r="D2" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E2">
         <v>8</v>
@@ -1944,7 +1989,7 @@
         <v>2021</v>
       </c>
       <c r="D3" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E3">
         <v>8</v>
@@ -1967,7 +2012,7 @@
         <v>2021</v>
       </c>
       <c r="D4" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -1990,7 +2035,7 @@
         <v>2021</v>
       </c>
       <c r="D5" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E5">
         <v>9</v>
@@ -2013,7 +2058,7 @@
         <v>2021</v>
       </c>
       <c r="D6" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -2036,7 +2081,7 @@
         <v>2021</v>
       </c>
       <c r="D7" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -2059,7 +2104,7 @@
         <v>2021</v>
       </c>
       <c r="D8" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -2082,7 +2127,7 @@
         <v>2021</v>
       </c>
       <c r="D9" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -2105,7 +2150,7 @@
         <v>2021</v>
       </c>
       <c r="D10" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E10">
         <v>9</v>
@@ -2128,7 +2173,7 @@
         <v>2021</v>
       </c>
       <c r="D11" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E11">
         <v>9</v>
@@ -2157,7 +2202,7 @@
         <v>2021</v>
       </c>
       <c r="D12" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E12">
         <v>13</v>
@@ -2192,7 +2237,7 @@
         <v>2021</v>
       </c>
       <c r="D13" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -2215,7 +2260,7 @@
         <v>2021</v>
       </c>
       <c r="D14" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E14">
         <v>9</v>
@@ -2238,7 +2283,7 @@
         <v>2021</v>
       </c>
       <c r="D15" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E15">
         <v>7</v>
@@ -2261,7 +2306,7 @@
         <v>2021</v>
       </c>
       <c r="D16" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E16">
         <v>8</v>
@@ -2284,7 +2329,7 @@
         <v>2021</v>
       </c>
       <c r="D17" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E17">
         <v>8</v>
@@ -2307,7 +2352,7 @@
         <v>2021</v>
       </c>
       <c r="D18" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -2330,7 +2375,7 @@
         <v>2021</v>
       </c>
       <c r="D19" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -2353,7 +2398,7 @@
         <v>2021</v>
       </c>
       <c r="D20" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E20">
         <v>8</v>
@@ -2376,7 +2421,7 @@
         <v>2021</v>
       </c>
       <c r="D21" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2399,7 +2444,7 @@
         <v>2021</v>
       </c>
       <c r="D22" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E22">
         <v>6</v>
@@ -2422,7 +2467,7 @@
         <v>2021</v>
       </c>
       <c r="D23" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E23">
         <v>8</v>
@@ -2445,7 +2490,7 @@
         <v>2021</v>
       </c>
       <c r="D24" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E24">
         <v>7</v>
@@ -2468,7 +2513,7 @@
         <v>2021</v>
       </c>
       <c r="D25" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -2491,7 +2536,7 @@
         <v>2021</v>
       </c>
       <c r="D26" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E26">
         <v>9</v>
@@ -2514,7 +2559,7 @@
         <v>2021</v>
       </c>
       <c r="D27" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E27">
         <v>3</v>
@@ -2537,7 +2582,7 @@
         <v>2021</v>
       </c>
       <c r="D28" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E28">
         <v>4</v>
@@ -2560,7 +2605,7 @@
         <v>2021</v>
       </c>
       <c r="D29" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -2583,7 +2628,7 @@
         <v>2021</v>
       </c>
       <c r="D30" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -2606,7 +2651,7 @@
         <v>2021</v>
       </c>
       <c r="D31" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -2629,7 +2674,7 @@
         <v>2021</v>
       </c>
       <c r="D32" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -2652,7 +2697,7 @@
         <v>2021</v>
       </c>
       <c r="D33" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E33">
         <v>5</v>
@@ -2675,7 +2720,7 @@
         <v>2021</v>
       </c>
       <c r="D34" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -2698,7 +2743,7 @@
         <v>2021</v>
       </c>
       <c r="D35" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E35">
         <v>11</v>
@@ -2733,7 +2778,7 @@
         <v>2021</v>
       </c>
       <c r="D36" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E36">
         <v>8</v>
@@ -2756,7 +2801,7 @@
         <v>2021</v>
       </c>
       <c r="D37" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E37">
         <v>9</v>
@@ -2779,7 +2824,7 @@
         <v>2021</v>
       </c>
       <c r="D38" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E38">
         <v>5</v>
@@ -2802,7 +2847,7 @@
         <v>2021</v>
       </c>
       <c r="D39" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E39">
         <v>2</v>
@@ -2825,7 +2870,7 @@
         <v>2021</v>
       </c>
       <c r="D40" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E40">
         <v>8</v>
@@ -2848,7 +2893,7 @@
         <v>2021</v>
       </c>
       <c r="D41" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E41">
         <v>7</v>
@@ -2871,7 +2916,7 @@
         <v>2021</v>
       </c>
       <c r="D42" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E42">
         <v>6</v>
@@ -2894,7 +2939,7 @@
         <v>2021</v>
       </c>
       <c r="D43" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E43">
         <v>7</v>
@@ -2917,7 +2962,7 @@
         <v>2021</v>
       </c>
       <c r="D44" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E44">
         <v>8</v>
@@ -2940,7 +2985,7 @@
         <v>2021</v>
       </c>
       <c r="D45" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E45">
         <v>7</v>
@@ -2963,7 +3008,7 @@
         <v>2021</v>
       </c>
       <c r="D46" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E46">
         <v>7</v>
@@ -2986,7 +3031,7 @@
         <v>2021</v>
       </c>
       <c r="D47" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E47">
         <v>5</v>
@@ -3009,7 +3054,7 @@
         <v>2021</v>
       </c>
       <c r="D48" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E48">
         <v>6</v>
@@ -3032,7 +3077,7 @@
         <v>2021</v>
       </c>
       <c r="D49" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E49">
         <v>6</v>
@@ -3055,7 +3100,7 @@
         <v>2021</v>
       </c>
       <c r="D50" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E50">
         <v>9</v>
@@ -3078,7 +3123,7 @@
         <v>2021</v>
       </c>
       <c r="D51" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E51">
         <v>8</v>
@@ -3101,7 +3146,7 @@
         <v>2021</v>
       </c>
       <c r="D52" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E52">
         <v>3</v>
@@ -3124,7 +3169,7 @@
         <v>2021</v>
       </c>
       <c r="D53" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E53">
         <v>11</v>
@@ -3159,7 +3204,7 @@
         <v>2021</v>
       </c>
       <c r="D54" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E54">
         <v>6</v>
@@ -3182,7 +3227,7 @@
         <v>2021</v>
       </c>
       <c r="D55" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E55">
         <v>4</v>
@@ -3205,7 +3250,7 @@
         <v>2021</v>
       </c>
       <c r="D56" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E56">
         <v>3</v>
@@ -3228,7 +3273,7 @@
         <v>2021</v>
       </c>
       <c r="D57" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E57">
         <v>6</v>
@@ -3251,7 +3296,7 @@
         <v>2021</v>
       </c>
       <c r="D58" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E58">
         <v>7</v>
@@ -3274,7 +3319,7 @@
         <v>2021</v>
       </c>
       <c r="D59" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E59">
         <v>4</v>
@@ -3297,7 +3342,7 @@
         <v>2021</v>
       </c>
       <c r="D60" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E60">
         <v>6</v>
@@ -3320,7 +3365,7 @@
         <v>2021</v>
       </c>
       <c r="D61" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E61">
         <v>6</v>
@@ -3343,7 +3388,7 @@
         <v>2021</v>
       </c>
       <c r="D62" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E62">
         <v>6</v>
@@ -3366,7 +3411,7 @@
         <v>2021</v>
       </c>
       <c r="D63" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E63">
         <v>4</v>
@@ -3389,7 +3434,7 @@
         <v>2021</v>
       </c>
       <c r="D64" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E64">
         <v>2</v>
@@ -3412,7 +3457,7 @@
         <v>2021</v>
       </c>
       <c r="D65" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E65">
         <v>8</v>
@@ -3435,7 +3480,7 @@
         <v>2021</v>
       </c>
       <c r="D66" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E66">
         <v>2</v>
@@ -3458,7 +3503,7 @@
         <v>2021</v>
       </c>
       <c r="D67" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E67">
         <v>8</v>
@@ -3481,7 +3526,7 @@
         <v>2021</v>
       </c>
       <c r="D68" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E68">
         <v>7</v>
@@ -3504,7 +3549,7 @@
         <v>2021</v>
       </c>
       <c r="D69" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E69">
         <v>4</v>
@@ -3527,7 +3572,7 @@
         <v>2021</v>
       </c>
       <c r="D70" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E70">
         <v>6</v>
@@ -3550,7 +3595,7 @@
         <v>2021</v>
       </c>
       <c r="D71" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E71">
         <v>7</v>
@@ -3573,7 +3618,7 @@
         <v>2021</v>
       </c>
       <c r="D72" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E72">
         <v>6</v>
@@ -3596,7 +3641,7 @@
         <v>2021</v>
       </c>
       <c r="D73" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E73">
         <v>3</v>
@@ -3619,7 +3664,7 @@
         <v>2021</v>
       </c>
       <c r="D74" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E74">
         <v>9</v>
@@ -3642,7 +3687,7 @@
         <v>2021</v>
       </c>
       <c r="D75" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E75">
         <v>9</v>
@@ -3665,7 +3710,7 @@
         <v>2021</v>
       </c>
       <c r="D76" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E76">
         <v>9</v>
@@ -3688,7 +3733,7 @@
         <v>2021</v>
       </c>
       <c r="D77" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E77">
         <v>4</v>
@@ -3711,7 +3756,7 @@
         <v>2021</v>
       </c>
       <c r="D78" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E78">
         <v>9</v>
@@ -3734,7 +3779,7 @@
         <v>2021</v>
       </c>
       <c r="D79" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E79">
         <v>8</v>
@@ -3757,7 +3802,7 @@
         <v>2021</v>
       </c>
       <c r="D80" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E80">
         <v>5</v>
@@ -3780,7 +3825,7 @@
         <v>2021</v>
       </c>
       <c r="D81" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="E81">
         <v>9</v>
@@ -3815,7 +3860,7 @@
         <v>2021</v>
       </c>
       <c r="D82" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E82">
         <v>8</v>
@@ -3838,7 +3883,7 @@
         <v>2021</v>
       </c>
       <c r="D83" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E83">
         <v>7</v>
@@ -3861,7 +3906,7 @@
         <v>2021</v>
       </c>
       <c r="D84" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E84">
         <v>5</v>
@@ -3884,7 +3929,7 @@
         <v>2021</v>
       </c>
       <c r="D85" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E85">
         <v>10</v>
@@ -3919,7 +3964,7 @@
         <v>2021</v>
       </c>
       <c r="D86" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E86">
         <v>8</v>
@@ -3942,7 +3987,7 @@
         <v>2021</v>
       </c>
       <c r="D87" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E87">
         <v>6</v>
@@ -3965,7 +4010,7 @@
         <v>2021</v>
       </c>
       <c r="D88" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E88">
         <v>4</v>
@@ -3988,7 +4033,7 @@
         <v>2021</v>
       </c>
       <c r="D89" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E89">
         <v>5</v>
@@ -4011,7 +4056,7 @@
         <v>2021</v>
       </c>
       <c r="D90" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E90">
         <v>9</v>
@@ -4034,7 +4079,7 @@
         <v>2021</v>
       </c>
       <c r="D91" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E91">
         <v>9</v>
@@ -4057,7 +4102,7 @@
         <v>2021</v>
       </c>
       <c r="D92" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E92">
         <v>3</v>
@@ -4077,7 +4122,7 @@
         <v>2021</v>
       </c>
       <c r="D93" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E93">
         <v>5</v>
@@ -4100,7 +4145,7 @@
         <v>2021</v>
       </c>
       <c r="D94" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E94">
         <v>7</v>
@@ -4123,7 +4168,7 @@
         <v>2021</v>
       </c>
       <c r="D95" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E95">
         <v>9</v>
@@ -4146,7 +4191,7 @@
         <v>2021</v>
       </c>
       <c r="D96" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E96">
         <v>6</v>
@@ -4169,7 +4214,7 @@
         <v>2021</v>
       </c>
       <c r="D97" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E97">
         <v>3</v>
@@ -4192,7 +4237,7 @@
         <v>2021</v>
       </c>
       <c r="D98" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E98">
         <v>5</v>
@@ -4215,7 +4260,7 @@
         <v>2021</v>
       </c>
       <c r="D99" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E99">
         <v>6</v>
@@ -4238,7 +4283,7 @@
         <v>2021</v>
       </c>
       <c r="D100" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E100">
         <v>8</v>
@@ -4261,7 +4306,7 @@
         <v>2021</v>
       </c>
       <c r="D101" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E101">
         <v>8</v>
@@ -4284,7 +4329,7 @@
         <v>2021</v>
       </c>
       <c r="D102" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E102">
         <v>10</v>
@@ -4319,7 +4364,7 @@
         <v>2021</v>
       </c>
       <c r="D103" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E103">
         <v>9</v>
@@ -4342,7 +4387,7 @@
         <v>2021</v>
       </c>
       <c r="D104" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E104">
         <v>4</v>
@@ -4365,7 +4410,7 @@
         <v>2021</v>
       </c>
       <c r="D105" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E105">
         <v>7</v>
@@ -4388,7 +4433,7 @@
         <v>2021</v>
       </c>
       <c r="D106" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E106">
         <v>8</v>
@@ -4411,7 +4456,7 @@
         <v>2021</v>
       </c>
       <c r="D107" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E107">
         <v>5</v>
@@ -4434,7 +4479,7 @@
         <v>2021</v>
       </c>
       <c r="D108" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E108">
         <v>6</v>
@@ -4457,7 +4502,7 @@
         <v>2021</v>
       </c>
       <c r="D109" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E109">
         <v>6</v>
@@ -4480,7 +4525,7 @@
         <v>2021</v>
       </c>
       <c r="D110" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E110">
         <v>5</v>
@@ -4503,7 +4548,7 @@
         <v>2021</v>
       </c>
       <c r="D111" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E111">
         <v>9</v>
@@ -4526,7 +4571,7 @@
         <v>2021</v>
       </c>
       <c r="D112" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E112">
         <v>6</v>
@@ -4549,7 +4594,7 @@
         <v>2021</v>
       </c>
       <c r="D113" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E113">
         <v>7</v>
@@ -4572,7 +4617,7 @@
         <v>2021</v>
       </c>
       <c r="D114" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E114">
         <v>8</v>
@@ -4595,7 +4640,7 @@
         <v>2021</v>
       </c>
       <c r="D115" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E115">
         <v>6</v>
@@ -4618,7 +4663,7 @@
         <v>2021</v>
       </c>
       <c r="D116" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E116">
         <v>7</v>
@@ -4641,7 +4686,7 @@
         <v>2021</v>
       </c>
       <c r="D117" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E117">
         <v>4</v>
@@ -4664,7 +4709,7 @@
         <v>2021</v>
       </c>
       <c r="D118" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E118">
         <v>6</v>
@@ -4687,7 +4732,7 @@
         <v>2021</v>
       </c>
       <c r="D119" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E119">
         <v>7</v>
@@ -4710,7 +4755,7 @@
         <v>2021</v>
       </c>
       <c r="D120" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E120">
         <v>6</v>
@@ -4733,7 +4778,7 @@
         <v>2021</v>
       </c>
       <c r="D121" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E121">
         <v>10</v>
@@ -4768,7 +4813,7 @@
         <v>2021</v>
       </c>
       <c r="D122" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E122">
         <v>9</v>
@@ -4791,7 +4836,7 @@
         <v>2021</v>
       </c>
       <c r="D123" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E123">
         <v>6</v>
@@ -4814,7 +4859,7 @@
         <v>2021</v>
       </c>
       <c r="D124" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E124">
         <v>8</v>
@@ -4837,7 +4882,7 @@
         <v>2021</v>
       </c>
       <c r="D125" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E125">
         <v>5</v>
@@ -4860,7 +4905,7 @@
         <v>2021</v>
       </c>
       <c r="D126" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E126">
         <v>9</v>
@@ -4883,7 +4928,7 @@
         <v>2021</v>
       </c>
       <c r="D127" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E127">
         <v>3</v>
@@ -4906,7 +4951,7 @@
         <v>2021</v>
       </c>
       <c r="D128" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E128">
         <v>8</v>
@@ -4929,7 +4974,7 @@
         <v>2021</v>
       </c>
       <c r="D129" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E129">
         <v>5</v>
@@ -4952,7 +4997,7 @@
         <v>2021</v>
       </c>
       <c r="D130" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E130">
         <v>9</v>
@@ -4975,7 +5020,7 @@
         <v>2021</v>
       </c>
       <c r="D131" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E131">
         <v>8</v>
@@ -4998,7 +5043,7 @@
         <v>2021</v>
       </c>
       <c r="D132" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E132">
         <v>9</v>
@@ -5021,7 +5066,7 @@
         <v>2021</v>
       </c>
       <c r="D133" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E133">
         <v>7</v>
@@ -5044,7 +5089,7 @@
         <v>2021</v>
       </c>
       <c r="D134" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E134">
         <v>6</v>
@@ -5067,7 +5112,7 @@
         <v>2021</v>
       </c>
       <c r="D135" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E135">
         <v>4</v>
@@ -5090,7 +5135,7 @@
         <v>2021</v>
       </c>
       <c r="D136" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E136">
         <v>8</v>
@@ -5113,7 +5158,7 @@
         <v>2021</v>
       </c>
       <c r="D137" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E137">
         <v>8</v>
@@ -5136,7 +5181,7 @@
         <v>2021</v>
       </c>
       <c r="D138" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E138">
         <v>6</v>
@@ -5159,7 +5204,7 @@
         <v>2021</v>
       </c>
       <c r="D139" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E139">
         <v>5</v>
@@ -5182,7 +5227,7 @@
         <v>2021</v>
       </c>
       <c r="D140" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E140">
         <v>6</v>
@@ -5205,7 +5250,7 @@
         <v>2021</v>
       </c>
       <c r="D141" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E141">
         <v>7</v>
@@ -5228,7 +5273,7 @@
         <v>2021</v>
       </c>
       <c r="D142" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E142">
         <v>6</v>
@@ -5251,7 +5296,7 @@
         <v>2021</v>
       </c>
       <c r="D143" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E143">
         <v>6</v>
@@ -5274,7 +5319,7 @@
         <v>2021</v>
       </c>
       <c r="D144" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E144">
         <v>4</v>
@@ -5297,7 +5342,7 @@
         <v>2021</v>
       </c>
       <c r="D145" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E145">
         <v>7</v>
@@ -5320,7 +5365,7 @@
         <v>2021</v>
       </c>
       <c r="D146" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E146">
         <v>8</v>
@@ -5343,7 +5388,7 @@
         <v>2021</v>
       </c>
       <c r="D147" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E147">
         <v>6</v>
@@ -5366,7 +5411,7 @@
         <v>2021</v>
       </c>
       <c r="D148" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E148">
         <v>8</v>
@@ -5389,7 +5434,7 @@
         <v>2021</v>
       </c>
       <c r="D149" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E149">
         <v>9</v>
@@ -5412,7 +5457,7 @@
         <v>2021</v>
       </c>
       <c r="D150" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E150">
         <v>5</v>
@@ -5435,7 +5480,7 @@
         <v>2021</v>
       </c>
       <c r="D151" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E151">
         <v>4</v>
@@ -5458,7 +5503,7 @@
         <v>2021</v>
       </c>
       <c r="D152" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E152">
         <v>9</v>
@@ -5481,7 +5526,7 @@
         <v>2021</v>
       </c>
       <c r="D153" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E153">
         <v>7</v>
@@ -5504,7 +5549,7 @@
         <v>2021</v>
       </c>
       <c r="D154" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E154">
         <v>4</v>
@@ -5527,7 +5572,7 @@
         <v>2021</v>
       </c>
       <c r="D155" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E155">
         <v>5</v>
@@ -5550,7 +5595,7 @@
         <v>2021</v>
       </c>
       <c r="D156" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E156">
         <v>9</v>
@@ -5573,7 +5618,7 @@
         <v>2021</v>
       </c>
       <c r="D157" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E157">
         <v>1</v>
@@ -5596,7 +5641,7 @@
         <v>2021</v>
       </c>
       <c r="D158" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E158">
         <v>2</v>
@@ -5619,7 +5664,7 @@
         <v>2021</v>
       </c>
       <c r="D159" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E159">
         <v>3</v>
@@ -5642,7 +5687,7 @@
         <v>2021</v>
       </c>
       <c r="D160" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E160">
         <v>3</v>
@@ -5665,7 +5710,7 @@
         <v>2021</v>
       </c>
       <c r="D161" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E161">
         <v>4</v>
@@ -5688,7 +5733,7 @@
         <v>2021</v>
       </c>
       <c r="D162" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E162">
         <v>7</v>
@@ -5711,7 +5756,7 @@
         <v>2021</v>
       </c>
       <c r="D163" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E163">
         <v>10</v>
@@ -5746,7 +5791,7 @@
         <v>2021</v>
       </c>
       <c r="D164" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E164">
         <v>9</v>
@@ -5769,7 +5814,7 @@
         <v>2021</v>
       </c>
       <c r="D165" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E165">
         <v>7</v>
@@ -5792,7 +5837,7 @@
         <v>2021</v>
       </c>
       <c r="D166" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E166">
         <v>6</v>
@@ -5815,7 +5860,7 @@
         <v>2021</v>
       </c>
       <c r="D167" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E167">
         <v>2</v>
@@ -5838,7 +5883,7 @@
         <v>2021</v>
       </c>
       <c r="D168" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E168">
         <v>4</v>
@@ -5861,7 +5906,7 @@
         <v>2021</v>
       </c>
       <c r="D169" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E169">
         <v>6</v>
@@ -5884,7 +5929,7 @@
         <v>2021</v>
       </c>
       <c r="D170" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E170">
         <v>4</v>
@@ -5907,7 +5952,7 @@
         <v>2021</v>
       </c>
       <c r="D171" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E171">
         <v>8</v>
@@ -5930,7 +5975,7 @@
         <v>2021</v>
       </c>
       <c r="D172" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E172">
         <v>2</v>
@@ -5953,7 +5998,7 @@
         <v>2021</v>
       </c>
       <c r="D173" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E173">
         <v>8</v>
@@ -5976,7 +6021,7 @@
         <v>2021</v>
       </c>
       <c r="D174" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E174">
         <v>3</v>
@@ -5999,7 +6044,7 @@
         <v>2021</v>
       </c>
       <c r="D175" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E175">
         <v>3</v>
@@ -6022,7 +6067,7 @@
         <v>2021</v>
       </c>
       <c r="D176" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E176">
         <v>4</v>
@@ -6045,7 +6090,7 @@
         <v>2021</v>
       </c>
       <c r="D177" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E177">
         <v>8</v>
@@ -6068,7 +6113,7 @@
         <v>2021</v>
       </c>
       <c r="D178" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E178">
         <v>3</v>
@@ -6091,7 +6136,7 @@
         <v>2021</v>
       </c>
       <c r="D179" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E179">
         <v>4</v>
@@ -6114,7 +6159,7 @@
         <v>2021</v>
       </c>
       <c r="D180" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E180">
         <v>6</v>
@@ -6137,7 +6182,7 @@
         <v>2021</v>
       </c>
       <c r="D181" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E181">
         <v>6</v>
@@ -6160,7 +6205,7 @@
         <v>2021</v>
       </c>
       <c r="D182" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E182">
         <v>8</v>
@@ -6183,7 +6228,7 @@
         <v>2021</v>
       </c>
       <c r="D183" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E183">
         <v>3</v>
@@ -6206,7 +6251,7 @@
         <v>2021</v>
       </c>
       <c r="D184" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E184">
         <v>8</v>
@@ -6229,7 +6274,7 @@
         <v>2021</v>
       </c>
       <c r="D185" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E185">
         <v>2</v>
@@ -6249,7 +6294,7 @@
         <v>2021</v>
       </c>
       <c r="D186" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E186">
         <v>10</v>
@@ -6284,7 +6329,7 @@
         <v>2021</v>
       </c>
       <c r="D187" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E187">
         <v>5</v>
@@ -6307,7 +6352,7 @@
         <v>2021</v>
       </c>
       <c r="D188" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E188">
         <v>8</v>
@@ -6330,7 +6375,7 @@
         <v>2021</v>
       </c>
       <c r="D189" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E189">
         <v>6</v>
@@ -6353,7 +6398,7 @@
         <v>2021</v>
       </c>
       <c r="D190" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E190">
         <v>5</v>
@@ -6376,7 +6421,7 @@
         <v>2021</v>
       </c>
       <c r="D191" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E191">
         <v>9</v>
@@ -6399,7 +6444,7 @@
         <v>2021</v>
       </c>
       <c r="D192" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E192">
         <v>7</v>
@@ -6422,7 +6467,7 @@
         <v>2021</v>
       </c>
       <c r="D193" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E193">
         <v>4</v>
@@ -6445,7 +6490,7 @@
         <v>2021</v>
       </c>
       <c r="D194" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E194">
         <v>2</v>
@@ -6468,7 +6513,7 @@
         <v>2021</v>
       </c>
       <c r="D195" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E195">
         <v>8</v>
@@ -6491,7 +6536,7 @@
         <v>2021</v>
       </c>
       <c r="D196" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E196">
         <v>4</v>
@@ -6514,7 +6559,7 @@
         <v>2021</v>
       </c>
       <c r="D197" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E197">
         <v>4</v>
@@ -6537,7 +6582,7 @@
         <v>2021</v>
       </c>
       <c r="D198" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E198">
         <v>11</v>
@@ -6572,7 +6617,7 @@
         <v>2021</v>
       </c>
       <c r="D199" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E199">
         <v>7</v>
@@ -6595,7 +6640,7 @@
         <v>2021</v>
       </c>
       <c r="D200" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E200">
         <v>10</v>
@@ -6630,7 +6675,7 @@
         <v>2021</v>
       </c>
       <c r="D201" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E201">
         <v>7</v>
@@ -6653,7 +6698,7 @@
         <v>2021</v>
       </c>
       <c r="D202" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E202">
         <v>8</v>
@@ -6676,7 +6721,7 @@
         <v>2021</v>
       </c>
       <c r="D203" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E203">
         <v>2</v>
@@ -6699,7 +6744,7 @@
         <v>2021</v>
       </c>
       <c r="D204" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E204">
         <v>4</v>
@@ -6722,7 +6767,7 @@
         <v>2021</v>
       </c>
       <c r="D205" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E205">
         <v>1</v>
@@ -6745,7 +6790,7 @@
         <v>2021</v>
       </c>
       <c r="D206" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E206">
         <v>8</v>
@@ -6768,7 +6813,7 @@
         <v>2021</v>
       </c>
       <c r="D207" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E207">
         <v>1</v>
@@ -6791,7 +6836,7 @@
         <v>2021</v>
       </c>
       <c r="D208" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E208">
         <v>7</v>
@@ -6814,7 +6859,7 @@
         <v>2021</v>
       </c>
       <c r="D209" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E209">
         <v>6</v>
@@ -6837,7 +6882,7 @@
         <v>2021</v>
       </c>
       <c r="D210" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E210">
         <v>7</v>
@@ -6860,7 +6905,7 @@
         <v>2021</v>
       </c>
       <c r="D211" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E211">
         <v>6</v>
@@ -6883,7 +6928,7 @@
         <v>2021</v>
       </c>
       <c r="D212" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E212">
         <v>5</v>
@@ -6906,7 +6951,7 @@
         <v>2021</v>
       </c>
       <c r="D213" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E213">
         <v>5</v>
@@ -6929,7 +6974,7 @@
         <v>2021</v>
       </c>
       <c r="D214" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E214">
         <v>8</v>
@@ -6952,7 +6997,7 @@
         <v>2021</v>
       </c>
       <c r="D215" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E215">
         <v>5</v>
@@ -6975,7 +7020,7 @@
         <v>2021</v>
       </c>
       <c r="D216" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E216">
         <v>9</v>
@@ -6998,7 +7043,7 @@
         <v>2021</v>
       </c>
       <c r="D217" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E217">
         <v>3</v>
@@ -7021,7 +7066,7 @@
         <v>2021</v>
       </c>
       <c r="D218" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E218">
         <v>4</v>
@@ -7044,7 +7089,7 @@
         <v>2021</v>
       </c>
       <c r="D219" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E219">
         <v>6</v>
@@ -7067,7 +7112,7 @@
         <v>2021</v>
       </c>
       <c r="D220" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E220">
         <v>5</v>
@@ -7090,7 +7135,7 @@
         <v>2021</v>
       </c>
       <c r="D221" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E221">
         <v>4</v>
@@ -7113,7 +7158,7 @@
         <v>2021</v>
       </c>
       <c r="D222" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E222">
         <v>5</v>
@@ -7136,7 +7181,7 @@
         <v>2021</v>
       </c>
       <c r="D223" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E223">
         <v>6</v>
@@ -7159,7 +7204,7 @@
         <v>2021</v>
       </c>
       <c r="D224" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E224">
         <v>4</v>
@@ -7182,7 +7227,7 @@
         <v>2021</v>
       </c>
       <c r="D225" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E225">
         <v>4</v>
@@ -7205,7 +7250,7 @@
         <v>2021</v>
       </c>
       <c r="D226" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E226">
         <v>8</v>
@@ -7228,7 +7273,7 @@
         <v>2021</v>
       </c>
       <c r="D227" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E227">
         <v>7</v>
@@ -7251,7 +7296,7 @@
         <v>2021</v>
       </c>
       <c r="D228" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E228">
         <v>9</v>
@@ -7274,7 +7319,7 @@
         <v>2021</v>
       </c>
       <c r="D229" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E229">
         <v>5</v>
@@ -7297,7 +7342,7 @@
         <v>2021</v>
       </c>
       <c r="D230" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E230">
         <v>8</v>
@@ -7320,7 +7365,7 @@
         <v>2021</v>
       </c>
       <c r="D231" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E231">
         <v>9</v>
@@ -7343,7 +7388,7 @@
         <v>2021</v>
       </c>
       <c r="D232" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E232">
         <v>6</v>
@@ -7366,7 +7411,7 @@
         <v>2021</v>
       </c>
       <c r="D233" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E233">
         <v>6</v>
@@ -7389,7 +7434,7 @@
         <v>2021</v>
       </c>
       <c r="D234" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E234">
         <v>6</v>
@@ -7412,7 +7457,7 @@
         <v>2021</v>
       </c>
       <c r="D235" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E235">
         <v>7</v>
@@ -7435,7 +7480,7 @@
         <v>2021</v>
       </c>
       <c r="D236" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E236">
         <v>9</v>
@@ -7458,7 +7503,7 @@
         <v>2021</v>
       </c>
       <c r="D237" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E237">
         <v>6</v>
@@ -7481,7 +7526,7 @@
         <v>2021</v>
       </c>
       <c r="D238" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E238">
         <v>8</v>
@@ -7504,7 +7549,7 @@
         <v>2021</v>
       </c>
       <c r="D239" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E239">
         <v>6</v>
@@ -7527,7 +7572,7 @@
         <v>2021</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E240">
         <v>5</v>
@@ -7550,7 +7595,7 @@
         <v>2021</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E241">
         <v>5</v>
@@ -7573,7 +7618,7 @@
         <v>2021</v>
       </c>
       <c r="D242" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E242">
         <v>6</v>
@@ -7596,7 +7641,7 @@
         <v>2021</v>
       </c>
       <c r="D243" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E243">
         <v>5</v>
@@ -7619,7 +7664,7 @@
         <v>2021</v>
       </c>
       <c r="D244" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E244">
         <v>8</v>
@@ -7642,7 +7687,7 @@
         <v>2021</v>
       </c>
       <c r="D245" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E245">
         <v>3</v>
@@ -7665,7 +7710,7 @@
         <v>2021</v>
       </c>
       <c r="D246" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E246">
         <v>7</v>
@@ -7688,7 +7733,7 @@
         <v>2021</v>
       </c>
       <c r="D247" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E247">
         <v>9</v>
@@ -7711,7 +7756,7 @@
         <v>2021</v>
       </c>
       <c r="D248" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E248">
         <v>8</v>
@@ -7734,7 +7779,7 @@
         <v>2021</v>
       </c>
       <c r="D249" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E249">
         <v>4</v>
@@ -7757,7 +7802,7 @@
         <v>2021</v>
       </c>
       <c r="D250" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E250">
         <v>6</v>
@@ -7780,7 +7825,7 @@
         <v>2021</v>
       </c>
       <c r="D251" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E251">
         <v>9</v>
@@ -7803,7 +7848,7 @@
         <v>2021</v>
       </c>
       <c r="D252" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E252">
         <v>3</v>
@@ -7826,7 +7871,7 @@
         <v>2021</v>
       </c>
       <c r="D253" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E253">
         <v>7</v>
@@ -7849,7 +7894,7 @@
         <v>2021</v>
       </c>
       <c r="D254" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E254">
         <v>9</v>
@@ -7872,7 +7917,7 @@
         <v>2021</v>
       </c>
       <c r="D255" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E255">
         <v>7</v>
@@ -7895,7 +7940,7 @@
         <v>2021</v>
       </c>
       <c r="D256" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E256">
         <v>9</v>
@@ -7918,7 +7963,7 @@
         <v>2021</v>
       </c>
       <c r="D257" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E257">
         <v>7</v>
@@ -7941,7 +7986,7 @@
         <v>2021</v>
       </c>
       <c r="D258" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E258">
         <v>4</v>
@@ -7964,7 +8009,7 @@
         <v>2021</v>
       </c>
       <c r="D259" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E259">
         <v>11</v>
@@ -7999,7 +8044,7 @@
         <v>2021</v>
       </c>
       <c r="D260" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E260">
         <v>10</v>
@@ -8034,7 +8079,7 @@
         <v>2021</v>
       </c>
       <c r="D261" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E261">
         <v>6</v>
@@ -8057,7 +8102,7 @@
         <v>2021</v>
       </c>
       <c r="D262" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E262">
         <v>9</v>
@@ -8080,7 +8125,7 @@
         <v>2021</v>
       </c>
       <c r="D263" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E263">
         <v>8</v>
@@ -8103,7 +8148,7 @@
         <v>2021</v>
       </c>
       <c r="D264" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E264">
         <v>8</v>
@@ -8126,7 +8171,7 @@
         <v>2021</v>
       </c>
       <c r="D265" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E265">
         <v>5</v>
@@ -8149,7 +8194,7 @@
         <v>2021</v>
       </c>
       <c r="D266" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E266">
         <v>9</v>
@@ -8172,7 +8217,7 @@
         <v>2021</v>
       </c>
       <c r="D267" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E267">
         <v>8</v>
@@ -8195,7 +8240,7 @@
         <v>2021</v>
       </c>
       <c r="D268" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E268">
         <v>2</v>
@@ -8218,7 +8263,7 @@
         <v>2021</v>
       </c>
       <c r="D269" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E269">
         <v>6</v>
@@ -8241,7 +8286,7 @@
         <v>2021</v>
       </c>
       <c r="D270" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E270">
         <v>10</v>
@@ -8276,7 +8321,7 @@
         <v>2021</v>
       </c>
       <c r="D271" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E271">
         <v>8</v>
@@ -8299,7 +8344,7 @@
         <v>2021</v>
       </c>
       <c r="D272" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E272">
         <v>7</v>
@@ -8322,7 +8367,7 @@
         <v>2021</v>
       </c>
       <c r="D273" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E273">
         <v>8</v>
@@ -8345,7 +8390,7 @@
         <v>2021</v>
       </c>
       <c r="D274" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E274">
         <v>9</v>
@@ -8368,7 +8413,7 @@
         <v>2021</v>
       </c>
       <c r="D275" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E275">
         <v>5</v>
@@ -8391,7 +8436,7 @@
         <v>2021</v>
       </c>
       <c r="D276" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E276">
         <v>9</v>
@@ -8414,7 +8459,7 @@
         <v>2021</v>
       </c>
       <c r="D277" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E277">
         <v>8</v>
@@ -8437,7 +8482,7 @@
         <v>2021</v>
       </c>
       <c r="D278" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E278">
         <v>9</v>
@@ -8460,7 +8505,7 @@
         <v>2021</v>
       </c>
       <c r="D279" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E279">
         <v>9</v>
@@ -8483,7 +8528,7 @@
         <v>2021</v>
       </c>
       <c r="D280" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E280">
         <v>7</v>
@@ -8506,7 +8551,7 @@
         <v>2021</v>
       </c>
       <c r="D281" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E281">
         <v>7</v>
@@ -8529,7 +8574,7 @@
         <v>2021</v>
       </c>
       <c r="D282" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E282">
         <v>6</v>
@@ -8552,7 +8597,7 @@
         <v>2021</v>
       </c>
       <c r="D283" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E283">
         <v>4</v>
@@ -8575,7 +8620,7 @@
         <v>2021</v>
       </c>
       <c r="D284" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E284">
         <v>6</v>
@@ -8598,7 +8643,7 @@
         <v>2021</v>
       </c>
       <c r="D285" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E285">
         <v>9</v>
@@ -8621,7 +8666,7 @@
         <v>2021</v>
       </c>
       <c r="D286" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E286">
         <v>7</v>
@@ -8644,7 +8689,7 @@
         <v>2021</v>
       </c>
       <c r="D287" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E287">
         <v>7</v>
@@ -8667,7 +8712,7 @@
         <v>2021</v>
       </c>
       <c r="D288" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E288">
         <v>7</v>
@@ -8690,7 +8735,7 @@
         <v>2021</v>
       </c>
       <c r="D289" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E289">
         <v>8</v>
@@ -8713,7 +8758,7 @@
         <v>2021</v>
       </c>
       <c r="D290" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E290">
         <v>6</v>
@@ -8736,7 +8781,7 @@
         <v>2021</v>
       </c>
       <c r="D291" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E291">
         <v>5</v>
@@ -8759,7 +8804,7 @@
         <v>2021</v>
       </c>
       <c r="D292" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E292">
         <v>8</v>
@@ -8782,7 +8827,7 @@
         <v>2021</v>
       </c>
       <c r="D293" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E293">
         <v>9</v>
@@ -8805,7 +8850,7 @@
         <v>2021</v>
       </c>
       <c r="D294" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E294">
         <v>6</v>
@@ -8828,7 +8873,7 @@
         <v>2021</v>
       </c>
       <c r="D295" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E295">
         <v>9</v>
@@ -8848,7 +8893,7 @@
         <v>2021</v>
       </c>
       <c r="D296" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E296">
         <v>8</v>
@@ -8871,7 +8916,7 @@
         <v>2021</v>
       </c>
       <c r="D297" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E297">
         <v>9</v>
@@ -8894,7 +8939,7 @@
         <v>2021</v>
       </c>
       <c r="D298" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E298">
         <v>3</v>
@@ -8917,7 +8962,7 @@
         <v>2021</v>
       </c>
       <c r="D299" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E299">
         <v>6</v>
@@ -8940,7 +8985,7 @@
         <v>2021</v>
       </c>
       <c r="D300" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E300">
         <v>6</v>
@@ -8963,7 +9008,7 @@
         <v>2021</v>
       </c>
       <c r="D301" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E301">
         <v>7</v>
@@ -8986,7 +9031,7 @@
         <v>2021</v>
       </c>
       <c r="D302" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E302">
         <v>7</v>
@@ -9009,7 +9054,7 @@
         <v>2021</v>
       </c>
       <c r="D303" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E303">
         <v>10</v>
@@ -9044,7 +9089,7 @@
         <v>2021</v>
       </c>
       <c r="D304" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E304">
         <v>9</v>
@@ -9067,7 +9112,7 @@
         <v>2021</v>
       </c>
       <c r="D305" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E305">
         <v>3</v>
@@ -9090,7 +9135,7 @@
         <v>2021</v>
       </c>
       <c r="D306" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E306">
         <v>9</v>
@@ -9113,7 +9158,7 @@
         <v>2021</v>
       </c>
       <c r="D307" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E307">
         <v>7</v>
@@ -9136,7 +9181,7 @@
         <v>2021</v>
       </c>
       <c r="D308" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E308">
         <v>2</v>
@@ -9159,7 +9204,7 @@
         <v>2021</v>
       </c>
       <c r="D309" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E309">
         <v>6</v>
@@ -9182,7 +9227,7 @@
         <v>2021</v>
       </c>
       <c r="D310" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E310">
         <v>6</v>
@@ -9205,7 +9250,7 @@
         <v>2021</v>
       </c>
       <c r="D311" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E311">
         <v>4</v>
@@ -9228,7 +9273,7 @@
         <v>2021</v>
       </c>
       <c r="D312" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E312">
         <v>1</v>
@@ -9251,7 +9296,7 @@
         <v>2021</v>
       </c>
       <c r="D313" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E313">
         <v>9</v>
@@ -9274,7 +9319,7 @@
         <v>2021</v>
       </c>
       <c r="D314" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E314">
         <v>5</v>
@@ -9297,7 +9342,7 @@
         <v>2021</v>
       </c>
       <c r="D315" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E315">
         <v>3</v>
@@ -9320,7 +9365,7 @@
         <v>2021</v>
       </c>
       <c r="D316" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E316">
         <v>6</v>
@@ -9343,7 +9388,7 @@
         <v>2021</v>
       </c>
       <c r="D317" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E317">
         <v>9</v>
@@ -9366,7 +9411,7 @@
         <v>2021</v>
       </c>
       <c r="D318" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E318">
         <v>6</v>
@@ -9389,7 +9434,7 @@
         <v>2021</v>
       </c>
       <c r="D319" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E319">
         <v>8</v>
@@ -9412,7 +9457,7 @@
         <v>2021</v>
       </c>
       <c r="D320" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E320">
         <v>2</v>
@@ -9435,7 +9480,7 @@
         <v>2021</v>
       </c>
       <c r="D321" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E321">
         <v>2</v>
@@ -9458,7 +9503,7 @@
         <v>2021</v>
       </c>
       <c r="D322" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E322">
         <v>4</v>
@@ -9481,7 +9526,7 @@
         <v>2021</v>
       </c>
       <c r="D323" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E323">
         <v>10</v>
@@ -9516,7 +9561,7 @@
         <v>2021</v>
       </c>
       <c r="D324" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E324">
         <v>9</v>
@@ -9539,7 +9584,7 @@
         <v>2021</v>
       </c>
       <c r="D325" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E325">
         <v>7</v>
@@ -9562,7 +9607,7 @@
         <v>2021</v>
       </c>
       <c r="D326" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E326">
         <v>10</v>
@@ -9597,7 +9642,7 @@
         <v>2021</v>
       </c>
       <c r="D327" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E327">
         <v>9</v>
@@ -9620,7 +9665,7 @@
         <v>2021</v>
       </c>
       <c r="D328" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E328">
         <v>9</v>
@@ -9643,7 +9688,7 @@
         <v>2021</v>
       </c>
       <c r="D329" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E329">
         <v>5</v>
@@ -9666,7 +9711,7 @@
         <v>2021</v>
       </c>
       <c r="D330" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E330">
         <v>5</v>
@@ -9689,7 +9734,7 @@
         <v>2021</v>
       </c>
       <c r="D331" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E331">
         <v>10</v>
@@ -9724,7 +9769,7 @@
         <v>2021</v>
       </c>
       <c r="D332" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E332">
         <v>6</v>
@@ -9747,7 +9792,7 @@
         <v>2021</v>
       </c>
       <c r="D333" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E333">
         <v>2</v>
@@ -9770,7 +9815,7 @@
         <v>2021</v>
       </c>
       <c r="D334" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E334">
         <v>7</v>
@@ -9793,7 +9838,7 @@
         <v>2021</v>
       </c>
       <c r="D335" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E335">
         <v>6</v>
@@ -9816,7 +9861,7 @@
         <v>2021</v>
       </c>
       <c r="D336" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E336">
         <v>6</v>
@@ -9839,7 +9884,7 @@
         <v>2021</v>
       </c>
       <c r="D337" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E337">
         <v>5</v>
@@ -9862,7 +9907,7 @@
         <v>2021</v>
       </c>
       <c r="D338" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E338">
         <v>2</v>
@@ -9885,7 +9930,7 @@
         <v>2021</v>
       </c>
       <c r="D339" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E339">
         <v>5</v>
@@ -9908,7 +9953,7 @@
         <v>2021</v>
       </c>
       <c r="D340" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E340">
         <v>9</v>
@@ -9931,7 +9976,7 @@
         <v>2021</v>
       </c>
       <c r="D341" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E341">
         <v>6</v>
@@ -9954,7 +9999,7 @@
         <v>2021</v>
       </c>
       <c r="D342" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E342">
         <v>7</v>
@@ -9977,7 +10022,7 @@
         <v>2021</v>
       </c>
       <c r="D343" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E343">
         <v>6</v>
@@ -10000,7 +10045,7 @@
         <v>2021</v>
       </c>
       <c r="D344" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E344">
         <v>9</v>
@@ -10023,7 +10068,7 @@
         <v>2021</v>
       </c>
       <c r="D345" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E345">
         <v>2</v>
@@ -10046,7 +10091,7 @@
         <v>2021</v>
       </c>
       <c r="D346" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E346">
         <v>9</v>
@@ -10069,7 +10114,7 @@
         <v>2021</v>
       </c>
       <c r="D347" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E347">
         <v>9</v>
@@ -10092,7 +10137,7 @@
         <v>2021</v>
       </c>
       <c r="D348" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E348">
         <v>5</v>
@@ -10115,7 +10160,7 @@
         <v>2021</v>
       </c>
       <c r="D349" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E349">
         <v>7</v>
@@ -10138,7 +10183,7 @@
         <v>2021</v>
       </c>
       <c r="D350" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E350">
         <v>9</v>
@@ -10161,7 +10206,7 @@
         <v>2021</v>
       </c>
       <c r="D351" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E351">
         <v>6</v>
@@ -10184,7 +10229,7 @@
         <v>2021</v>
       </c>
       <c r="D352" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E352">
         <v>6</v>
@@ -10207,7 +10252,7 @@
         <v>2021</v>
       </c>
       <c r="D353" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E353">
         <v>4</v>
@@ -10230,7 +10275,7 @@
         <v>2021</v>
       </c>
       <c r="D354" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E354">
         <v>9</v>
@@ -10253,7 +10298,7 @@
         <v>2021</v>
       </c>
       <c r="D355" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E355">
         <v>6</v>
@@ -10276,7 +10321,7 @@
         <v>2021</v>
       </c>
       <c r="D356" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E356">
         <v>5</v>
@@ -10299,7 +10344,7 @@
         <v>2021</v>
       </c>
       <c r="D357" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E357">
         <v>8</v>
@@ -10322,7 +10367,7 @@
         <v>2021</v>
       </c>
       <c r="D358" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E358">
         <v>8</v>
@@ -10345,7 +10390,7 @@
         <v>2021</v>
       </c>
       <c r="D359" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E359">
         <v>5</v>
@@ -10368,7 +10413,7 @@
         <v>2021</v>
       </c>
       <c r="D360" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E360">
         <v>2</v>
@@ -10391,7 +10436,7 @@
         <v>2021</v>
       </c>
       <c r="D361" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E361">
         <v>6</v>
@@ -10414,7 +10459,7 @@
         <v>2021</v>
       </c>
       <c r="D362" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E362">
         <v>8</v>
@@ -10437,7 +10482,7 @@
         <v>2021</v>
       </c>
       <c r="D363" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E363">
         <v>8</v>
@@ -10460,7 +10505,7 @@
         <v>2021</v>
       </c>
       <c r="D364" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E364">
         <v>4</v>
@@ -10483,7 +10528,7 @@
         <v>2021</v>
       </c>
       <c r="D365" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E365">
         <v>7</v>
@@ -10506,7 +10551,7 @@
         <v>2021</v>
       </c>
       <c r="D366" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E366">
         <v>6</v>
@@ -10529,7 +10574,7 @@
         <v>2021</v>
       </c>
       <c r="D367" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E367">
         <v>8</v>
@@ -10552,7 +10597,7 @@
         <v>2021</v>
       </c>
       <c r="D368" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E368">
         <v>5</v>
@@ -10575,7 +10620,7 @@
         <v>2021</v>
       </c>
       <c r="D369" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E369">
         <v>7</v>
@@ -10598,7 +10643,7 @@
         <v>2021</v>
       </c>
       <c r="D370" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E370">
         <v>7</v>
@@ -10618,7 +10663,7 @@
         <v>2021</v>
       </c>
       <c r="D371" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E371">
         <v>9</v>
@@ -10641,7 +10686,7 @@
         <v>2021</v>
       </c>
       <c r="D372" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E372">
         <v>4</v>
@@ -10664,7 +10709,7 @@
         <v>2021</v>
       </c>
       <c r="D373" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E373">
         <v>5</v>
@@ -10687,7 +10732,7 @@
         <v>2021</v>
       </c>
       <c r="D374" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E374">
         <v>5</v>
@@ -10710,7 +10755,7 @@
         <v>2021</v>
       </c>
       <c r="D375" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E375">
         <v>4</v>
@@ -10733,7 +10778,7 @@
         <v>2021</v>
       </c>
       <c r="D376" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E376">
         <v>9</v>
@@ -10756,7 +10801,7 @@
         <v>2021</v>
       </c>
       <c r="D377" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E377">
         <v>9</v>
@@ -10779,7 +10824,7 @@
         <v>2021</v>
       </c>
       <c r="D378" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E378">
         <v>8</v>
@@ -10802,7 +10847,7 @@
         <v>2021</v>
       </c>
       <c r="D379" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E379">
         <v>8</v>
@@ -10825,7 +10870,7 @@
         <v>2021</v>
       </c>
       <c r="D380" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E380">
         <v>6</v>
@@ -10848,7 +10893,7 @@
         <v>2021</v>
       </c>
       <c r="D381" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E381">
         <v>6</v>
@@ -10871,7 +10916,7 @@
         <v>2021</v>
       </c>
       <c r="D382" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E382">
         <v>6</v>
@@ -10894,7 +10939,7 @@
         <v>2021</v>
       </c>
       <c r="D383" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E383">
         <v>7</v>
@@ -10917,7 +10962,7 @@
         <v>2021</v>
       </c>
       <c r="D384" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E384">
         <v>8</v>
@@ -10940,7 +10985,7 @@
         <v>2021</v>
       </c>
       <c r="D385" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E385">
         <v>3</v>
@@ -10963,7 +11008,7 @@
         <v>2021</v>
       </c>
       <c r="D386" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E386">
         <v>6</v>
@@ -10986,7 +11031,7 @@
         <v>2021</v>
       </c>
       <c r="D387" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E387">
         <v>6</v>
@@ -11009,7 +11054,7 @@
         <v>2021</v>
       </c>
       <c r="D388" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E388">
         <v>8</v>
@@ -11032,7 +11077,7 @@
         <v>2021</v>
       </c>
       <c r="D389" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E389">
         <v>6</v>
@@ -11055,7 +11100,7 @@
         <v>2022</v>
       </c>
       <c r="D390" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E390">
         <v>4</v>
@@ -11078,7 +11123,7 @@
         <v>2022</v>
       </c>
       <c r="D391" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E391">
         <v>4</v>
@@ -11101,7 +11146,7 @@
         <v>2022</v>
       </c>
       <c r="D392" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E392">
         <v>4</v>
@@ -11124,7 +11169,7 @@
         <v>2022</v>
       </c>
       <c r="D393" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E393">
         <v>5</v>
@@ -11159,7 +11204,7 @@
         <v>2022</v>
       </c>
       <c r="D394" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E394">
         <v>2</v>
@@ -11182,7 +11227,7 @@
         <v>2022</v>
       </c>
       <c r="D395" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E395">
         <v>3</v>
@@ -11205,7 +11250,7 @@
         <v>2022</v>
       </c>
       <c r="D396" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E396">
         <v>4</v>
@@ -11228,7 +11273,7 @@
         <v>2022</v>
       </c>
       <c r="D397" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E397">
         <v>4</v>
@@ -11251,7 +11296,7 @@
         <v>2022</v>
       </c>
       <c r="D398" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E398">
         <v>4</v>
@@ -11274,7 +11319,7 @@
         <v>2022</v>
       </c>
       <c r="D399" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E399">
         <v>3</v>
@@ -11297,7 +11342,7 @@
         <v>2022</v>
       </c>
       <c r="D400" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E400">
         <v>5</v>
@@ -11332,7 +11377,7 @@
         <v>2022</v>
       </c>
       <c r="D401" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E401">
         <v>3</v>
@@ -11355,7 +11400,7 @@
         <v>2022</v>
       </c>
       <c r="D402" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E402">
         <v>4</v>
@@ -11378,7 +11423,7 @@
         <v>2022</v>
       </c>
       <c r="D403" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E403">
         <v>3</v>
@@ -11401,7 +11446,7 @@
         <v>2022</v>
       </c>
       <c r="D404" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E404">
         <v>4</v>
@@ -11424,7 +11469,7 @@
         <v>2022</v>
       </c>
       <c r="D405" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E405">
         <v>2</v>
@@ -11447,7 +11492,7 @@
         <v>2022</v>
       </c>
       <c r="D406" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E406">
         <v>4</v>
@@ -11470,7 +11515,7 @@
         <v>2022</v>
       </c>
       <c r="D407" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E407">
         <v>1</v>
@@ -11493,7 +11538,7 @@
         <v>2022</v>
       </c>
       <c r="D408" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E408">
         <v>4</v>
@@ -11516,7 +11561,7 @@
         <v>2022</v>
       </c>
       <c r="D409" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E409">
         <v>4</v>
@@ -11539,7 +11584,7 @@
         <v>2022</v>
       </c>
       <c r="D410" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E410">
         <v>2</v>
@@ -11562,7 +11607,7 @@
         <v>2022</v>
       </c>
       <c r="D411" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E411">
         <v>2</v>
@@ -11585,7 +11630,7 @@
         <v>2022</v>
       </c>
       <c r="D412" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E412">
         <v>3</v>
@@ -11608,7 +11653,7 @@
         <v>2022</v>
       </c>
       <c r="D413" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E413">
         <v>3</v>
@@ -11631,7 +11676,7 @@
         <v>2022</v>
       </c>
       <c r="D414" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E414">
         <v>4</v>
@@ -11654,7 +11699,7 @@
         <v>2022</v>
       </c>
       <c r="D415" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E415">
         <v>3</v>
@@ -11677,7 +11722,7 @@
         <v>2022</v>
       </c>
       <c r="D416" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E416">
         <v>4</v>
@@ -11700,7 +11745,7 @@
         <v>2022</v>
       </c>
       <c r="D417" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E417">
         <v>4</v>
@@ -11723,7 +11768,7 @@
         <v>2022</v>
       </c>
       <c r="D418" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E418">
         <v>1</v>
@@ -11746,7 +11791,7 @@
         <v>2022</v>
       </c>
       <c r="D419" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E419">
         <v>1</v>
@@ -11766,7 +11811,7 @@
         <v>2022</v>
       </c>
       <c r="D420" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E420">
         <v>2</v>
@@ -11789,7 +11834,7 @@
         <v>2022</v>
       </c>
       <c r="D421" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E421">
         <v>2</v>
@@ -11812,7 +11857,7 @@
         <v>2022</v>
       </c>
       <c r="D422" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E422">
         <v>1</v>
@@ -11835,7 +11880,7 @@
         <v>2022</v>
       </c>
       <c r="D423" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E423">
         <v>1</v>
@@ -11858,7 +11903,7 @@
         <v>2022</v>
       </c>
       <c r="D424" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E424">
         <v>1</v>
@@ -11881,7 +11926,7 @@
         <v>2022</v>
       </c>
       <c r="D425" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E425">
         <v>4</v>
@@ -11904,7 +11949,7 @@
         <v>2022</v>
       </c>
       <c r="D426" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E426">
         <v>1</v>
@@ -11927,7 +11972,7 @@
         <v>2022</v>
       </c>
       <c r="D427" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E427">
         <v>3</v>
@@ -11950,7 +11995,7 @@
         <v>2022</v>
       </c>
       <c r="D428" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E428">
         <v>4</v>
@@ -11973,7 +12018,7 @@
         <v>2022</v>
       </c>
       <c r="D429" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E429">
         <v>4</v>
@@ -11996,7 +12041,7 @@
         <v>2022</v>
       </c>
       <c r="D430" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E430">
         <v>4</v>
@@ -12019,7 +12064,7 @@
         <v>2022</v>
       </c>
       <c r="D431" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E431">
         <v>4</v>
@@ -12042,7 +12087,7 @@
         <v>2022</v>
       </c>
       <c r="D432" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E432">
         <v>4</v>
@@ -12065,7 +12110,7 @@
         <v>2022</v>
       </c>
       <c r="D433" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E433">
         <v>4</v>
@@ -12088,7 +12133,7 @@
         <v>2022</v>
       </c>
       <c r="D434" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E434">
         <v>1</v>
@@ -12108,7 +12153,7 @@
         <v>2022</v>
       </c>
       <c r="D435" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E435">
         <v>8</v>
@@ -12140,7 +12185,7 @@
         <v>2022</v>
       </c>
       <c r="D436" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E436">
         <v>2</v>
@@ -12163,7 +12208,7 @@
         <v>2022</v>
       </c>
       <c r="D437" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E437">
         <v>1</v>
@@ -12186,7 +12231,7 @@
         <v>2022</v>
       </c>
       <c r="D438" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E438">
         <v>2</v>
@@ -12209,7 +12254,7 @@
         <v>2022</v>
       </c>
       <c r="D439" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E439">
         <v>1</v>
@@ -12232,7 +12277,7 @@
         <v>2022</v>
       </c>
       <c r="D440" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E440">
         <v>1</v>
@@ -12255,7 +12300,7 @@
         <v>2022</v>
       </c>
       <c r="D441" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E441">
         <v>2</v>
@@ -12278,7 +12323,7 @@
         <v>2022</v>
       </c>
       <c r="D442" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E442">
         <v>3</v>
@@ -12301,7 +12346,7 @@
         <v>2022</v>
       </c>
       <c r="D443" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E443">
         <v>3</v>
@@ -12324,7 +12369,7 @@
         <v>2022</v>
       </c>
       <c r="D444" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E444">
         <v>2</v>
@@ -12347,7 +12392,7 @@
         <v>2022</v>
       </c>
       <c r="D445" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E445">
         <v>1</v>
@@ -12370,7 +12415,7 @@
         <v>2022</v>
       </c>
       <c r="D446" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E446">
         <v>3</v>
@@ -12393,7 +12438,7 @@
         <v>2022</v>
       </c>
       <c r="D447" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E447">
         <v>4</v>
@@ -12416,7 +12461,7 @@
         <v>2022</v>
       </c>
       <c r="D448" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E448">
         <v>2</v>
@@ -12445,7 +12490,7 @@
         <v>2022</v>
       </c>
       <c r="D449" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E449">
         <v>2</v>
@@ -12468,7 +12513,7 @@
         <v>2022</v>
       </c>
       <c r="D450" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E450">
         <v>1</v>
@@ -12491,7 +12536,7 @@
         <v>2022</v>
       </c>
       <c r="D451" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E451">
         <v>3</v>
@@ -12514,7 +12559,7 @@
         <v>2022</v>
       </c>
       <c r="D452" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E452">
         <v>4</v>
@@ -12537,7 +12582,7 @@
         <v>2022</v>
       </c>
       <c r="D453" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E453">
         <v>2</v>
@@ -12560,7 +12605,7 @@
         <v>2022</v>
       </c>
       <c r="D454" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E454">
         <v>3</v>
@@ -12583,7 +12628,7 @@
         <v>2022</v>
       </c>
       <c r="D455" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E455">
         <v>4</v>
@@ -12606,7 +12651,7 @@
         <v>2022</v>
       </c>
       <c r="D456" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E456">
         <v>1</v>
@@ -12629,7 +12674,7 @@
         <v>2022</v>
       </c>
       <c r="D457" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E457">
         <v>2</v>
@@ -12652,7 +12697,7 @@
         <v>2022</v>
       </c>
       <c r="D458" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E458">
         <v>4</v>
@@ -12675,7 +12720,7 @@
         <v>2022</v>
       </c>
       <c r="D459" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E459">
         <v>3</v>
@@ -12698,7 +12743,7 @@
         <v>2022</v>
       </c>
       <c r="D460" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E460">
         <v>2</v>
@@ -12721,7 +12766,7 @@
         <v>2023</v>
       </c>
       <c r="D461" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E461">
         <v>3</v>
@@ -12744,7 +12789,7 @@
         <v>2023</v>
       </c>
       <c r="D462" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E462">
         <v>4</v>
@@ -12767,7 +12812,7 @@
         <v>2023</v>
       </c>
       <c r="D463" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E463">
         <v>4</v>
@@ -12790,7 +12835,7 @@
         <v>2023</v>
       </c>
       <c r="D464" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E464">
         <v>3</v>
@@ -12813,7 +12858,7 @@
         <v>2023</v>
       </c>
       <c r="D465" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E465">
         <v>3</v>
@@ -12836,7 +12881,7 @@
         <v>2023</v>
       </c>
       <c r="D466" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E466">
         <v>4</v>
@@ -12859,7 +12904,7 @@
         <v>2023</v>
       </c>
       <c r="D467" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E467">
         <v>3</v>
@@ -12882,7 +12927,7 @@
         <v>2023</v>
       </c>
       <c r="D468" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E468">
         <v>12</v>
@@ -12914,7 +12959,7 @@
         <v>2023</v>
       </c>
       <c r="D469" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E469">
         <v>4</v>
@@ -12937,7 +12982,7 @@
         <v>2023</v>
       </c>
       <c r="D470" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E470">
         <v>2</v>
@@ -12960,7 +13005,7 @@
         <v>2023</v>
       </c>
       <c r="D471" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E471">
         <v>1</v>
@@ -12983,7 +13028,7 @@
         <v>2023</v>
       </c>
       <c r="D472" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="E472">
         <v>3</v>
@@ -13018,7 +13063,7 @@
         <v>2023</v>
       </c>
       <c r="D473" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E473">
         <v>4</v>
@@ -13041,7 +13086,7 @@
         <v>2023</v>
       </c>
       <c r="D474" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E474">
         <v>3</v>
@@ -13064,7 +13109,7 @@
         <v>2023</v>
       </c>
       <c r="D475" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E475">
         <v>4</v>
@@ -13087,7 +13132,7 @@
         <v>2023</v>
       </c>
       <c r="D476" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E476">
         <v>4</v>
@@ -13110,7 +13155,7 @@
         <v>2023</v>
       </c>
       <c r="D477" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E477">
         <v>4</v>
@@ -13133,7 +13178,7 @@
         <v>2023</v>
       </c>
       <c r="D478" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E478">
         <v>1</v>
@@ -13156,7 +13201,7 @@
         <v>2023</v>
       </c>
       <c r="D479" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E479">
         <v>4</v>
@@ -13179,7 +13224,7 @@
         <v>2023</v>
       </c>
       <c r="D480" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E480">
         <v>7</v>
@@ -13214,7 +13259,7 @@
         <v>2023</v>
       </c>
       <c r="D481" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E481">
         <v>4</v>
@@ -13237,7 +13282,7 @@
         <v>2023</v>
       </c>
       <c r="D482" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E482">
         <v>3</v>
@@ -13260,7 +13305,7 @@
         <v>2023</v>
       </c>
       <c r="D483" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E483">
         <v>3</v>
@@ -13289,7 +13334,7 @@
         <v>2023</v>
       </c>
       <c r="D484" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E484">
         <v>4</v>
@@ -13312,7 +13357,7 @@
         <v>2023</v>
       </c>
       <c r="D485" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E485">
         <v>2</v>
@@ -13335,7 +13380,7 @@
         <v>2023</v>
       </c>
       <c r="D486" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E486">
         <v>4</v>
@@ -13358,7 +13403,7 @@
         <v>2023</v>
       </c>
       <c r="D487" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E487">
         <v>2</v>
@@ -13381,7 +13426,7 @@
         <v>2023</v>
       </c>
       <c r="D488" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E488">
         <v>6</v>
@@ -13416,7 +13461,7 @@
         <v>2023</v>
       </c>
       <c r="D489" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E489">
         <v>4</v>
@@ -13439,7 +13484,7 @@
         <v>2023</v>
       </c>
       <c r="D490" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E490">
         <v>4</v>
@@ -13462,7 +13507,7 @@
         <v>2023</v>
       </c>
       <c r="D491" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E491">
         <v>4</v>
@@ -13485,7 +13530,7 @@
         <v>2023</v>
       </c>
       <c r="D492" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E492">
         <v>4</v>
@@ -13508,7 +13553,7 @@
         <v>2023</v>
       </c>
       <c r="D493" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E493">
         <v>2</v>
@@ -13531,7 +13576,7 @@
         <v>2023</v>
       </c>
       <c r="D494" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E494">
         <v>11</v>
@@ -13566,7 +13611,7 @@
         <v>2023</v>
       </c>
       <c r="D495" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E495">
         <v>4</v>
@@ -13589,7 +13634,7 @@
         <v>2023</v>
       </c>
       <c r="D496" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E496">
         <v>4</v>
@@ -13612,7 +13657,7 @@
         <v>2023</v>
       </c>
       <c r="D497" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E497">
         <v>8</v>
@@ -13647,7 +13692,7 @@
         <v>2023</v>
       </c>
       <c r="D498" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E498">
         <v>5</v>
@@ -13682,7 +13727,7 @@
         <v>2023</v>
       </c>
       <c r="D499" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E499">
         <v>1</v>
@@ -13705,7 +13750,7 @@
         <v>2023</v>
       </c>
       <c r="D500" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E500">
         <v>2</v>
@@ -13728,7 +13773,7 @@
         <v>2023</v>
       </c>
       <c r="D501" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E501">
         <v>2</v>
@@ -13751,7 +13796,7 @@
         <v>2023</v>
       </c>
       <c r="D502" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E502">
         <v>6</v>
@@ -13786,7 +13831,7 @@
         <v>2023</v>
       </c>
       <c r="D503" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E503">
         <v>2</v>
@@ -13809,7 +13854,7 @@
         <v>2023</v>
       </c>
       <c r="D504" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E504">
         <v>3</v>
@@ -13832,7 +13877,7 @@
         <v>2023</v>
       </c>
       <c r="D505" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="E505">
         <v>4</v>
@@ -13867,7 +13912,7 @@
         <v>2023</v>
       </c>
       <c r="D506" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E506">
         <v>3</v>
@@ -13890,7 +13935,7 @@
         <v>2023</v>
       </c>
       <c r="D507" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E507">
         <v>4</v>
@@ -13913,7 +13958,7 @@
         <v>2023</v>
       </c>
       <c r="D508" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E508">
         <v>4</v>
@@ -13936,7 +13981,7 @@
         <v>2023</v>
       </c>
       <c r="D509" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E509">
         <v>3</v>
@@ -13965,7 +14010,7 @@
         <v>2023</v>
       </c>
       <c r="D510" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E510">
         <v>2</v>
@@ -13988,7 +14033,7 @@
         <v>2023</v>
       </c>
       <c r="D511" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E511">
         <v>1</v>
@@ -14011,7 +14056,7 @@
         <v>2023</v>
       </c>
       <c r="D512" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E512">
         <v>1</v>
@@ -14034,7 +14079,7 @@
         <v>2023</v>
       </c>
       <c r="D513" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E513">
         <v>3</v>
@@ -14057,7 +14102,7 @@
         <v>2023</v>
       </c>
       <c r="D514" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E514">
         <v>4</v>
@@ -14080,7 +14125,7 @@
         <v>2023</v>
       </c>
       <c r="D515" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E515">
         <v>5</v>
@@ -14115,7 +14160,7 @@
         <v>2023</v>
       </c>
       <c r="D516" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E516">
         <v>4</v>
@@ -14138,7 +14183,7 @@
         <v>2023</v>
       </c>
       <c r="D517" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E517">
         <v>4</v>
@@ -14161,7 +14206,7 @@
         <v>2023</v>
       </c>
       <c r="D518" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E518">
         <v>1</v>
@@ -14184,7 +14229,7 @@
         <v>2023</v>
       </c>
       <c r="D519" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E519">
         <v>6</v>
@@ -14219,7 +14264,7 @@
         <v>2023</v>
       </c>
       <c r="D520" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E520">
         <v>3</v>
@@ -14242,7 +14287,7 @@
         <v>2023</v>
       </c>
       <c r="D521" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E521">
         <v>3</v>
@@ -14265,7 +14310,7 @@
         <v>2023</v>
       </c>
       <c r="D522" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E522">
         <v>4</v>
@@ -14288,7 +14333,7 @@
         <v>2023</v>
       </c>
       <c r="D523" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E523">
         <v>2</v>
@@ -14311,7 +14356,7 @@
         <v>2024</v>
       </c>
       <c r="D524" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E524">
         <v>4</v>
@@ -14334,7 +14379,7 @@
         <v>2024</v>
       </c>
       <c r="D525" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E525">
         <v>1</v>
@@ -14357,7 +14402,7 @@
         <v>2024</v>
       </c>
       <c r="D526" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E526">
         <v>4</v>
@@ -14380,7 +14425,7 @@
         <v>2024</v>
       </c>
       <c r="D527" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E527">
         <v>2</v>
@@ -14403,7 +14448,7 @@
         <v>2024</v>
       </c>
       <c r="D528" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E528">
         <v>3</v>
@@ -14426,7 +14471,7 @@
         <v>2024</v>
       </c>
       <c r="D529" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E529">
         <v>3</v>
@@ -14449,7 +14494,7 @@
         <v>2024</v>
       </c>
       <c r="D530" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E530">
         <v>8</v>
@@ -14484,7 +14529,7 @@
         <v>2024</v>
       </c>
       <c r="D531" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E531">
         <v>3</v>
@@ -14507,7 +14552,7 @@
         <v>2024</v>
       </c>
       <c r="D532" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E532">
         <v>2</v>
@@ -14530,7 +14575,7 @@
         <v>2024</v>
       </c>
       <c r="D533" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E533">
         <v>2</v>
@@ -14553,7 +14598,7 @@
         <v>2024</v>
       </c>
       <c r="D534" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E534">
         <v>4</v>
@@ -14576,7 +14621,7 @@
         <v>2024</v>
       </c>
       <c r="D535" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E535">
         <v>3</v>
@@ -14599,7 +14644,7 @@
         <v>2024</v>
       </c>
       <c r="D536" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E536">
         <v>2</v>
@@ -14622,7 +14667,7 @@
         <v>2024</v>
       </c>
       <c r="D537" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E537">
         <v>4</v>
@@ -14645,7 +14690,7 @@
         <v>2024</v>
       </c>
       <c r="D538" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E538">
         <v>3</v>
@@ -14668,7 +14713,7 @@
         <v>2024</v>
       </c>
       <c r="D539" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E539">
         <v>5</v>
@@ -14703,7 +14748,7 @@
         <v>2024</v>
       </c>
       <c r="D540" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E540">
         <v>4</v>
@@ -14726,7 +14771,7 @@
         <v>2024</v>
       </c>
       <c r="D541" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E541">
         <v>1</v>
@@ -14749,7 +14794,7 @@
         <v>2024</v>
       </c>
       <c r="D542" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E542">
         <v>4</v>
@@ -14772,7 +14817,7 @@
         <v>2024</v>
       </c>
       <c r="D543" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E543">
         <v>3</v>
@@ -14795,7 +14840,7 @@
         <v>2024</v>
       </c>
       <c r="D544" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E544">
         <v>3</v>
@@ -14818,7 +14863,7 @@
         <v>2024</v>
       </c>
       <c r="D545" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E545">
         <v>4</v>
@@ -14841,7 +14886,7 @@
         <v>2024</v>
       </c>
       <c r="D546" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E546">
         <v>3</v>
@@ -14864,7 +14909,7 @@
         <v>2024</v>
       </c>
       <c r="D547" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E547">
         <v>2</v>
@@ -14887,7 +14932,7 @@
         <v>2024</v>
       </c>
       <c r="D548" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E548">
         <v>6</v>
@@ -14919,7 +14964,7 @@
         <v>2024</v>
       </c>
       <c r="D549" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E549">
         <v>3</v>
@@ -14942,7 +14987,7 @@
         <v>2024</v>
       </c>
       <c r="D550" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E550">
         <v>3</v>
@@ -14965,7 +15010,7 @@
         <v>2024</v>
       </c>
       <c r="D551" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E551">
         <v>1</v>
@@ -14988,7 +15033,7 @@
         <v>2024</v>
       </c>
       <c r="D552" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E552">
         <v>4</v>
@@ -15011,7 +15056,7 @@
         <v>2024</v>
       </c>
       <c r="D553" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E553">
         <v>3</v>
@@ -15034,7 +15079,7 @@
         <v>2024</v>
       </c>
       <c r="D554" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E554">
         <v>4</v>
@@ -15063,7 +15108,7 @@
         <v>2024</v>
       </c>
       <c r="D555" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E555">
         <v>3</v>
@@ -15086,7 +15131,7 @@
         <v>2024</v>
       </c>
       <c r="D556" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E556">
         <v>1</v>
@@ -15109,7 +15154,7 @@
         <v>2024</v>
       </c>
       <c r="D557" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E557">
         <v>3</v>
@@ -15132,7 +15177,7 @@
         <v>2024</v>
       </c>
       <c r="D558" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E558">
         <v>2</v>
@@ -15155,7 +15200,7 @@
         <v>2024</v>
       </c>
       <c r="D559" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E559">
         <v>3</v>
@@ -15178,7 +15223,7 @@
         <v>2024</v>
       </c>
       <c r="D560" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E560">
         <v>2</v>
@@ -15201,7 +15246,7 @@
         <v>2024</v>
       </c>
       <c r="D561" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E561">
         <v>2</v>
@@ -15224,7 +15269,7 @@
         <v>2024</v>
       </c>
       <c r="D562" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E562">
         <v>3</v>
@@ -15247,7 +15292,7 @@
         <v>2024</v>
       </c>
       <c r="D563" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E563">
         <v>4</v>
@@ -15270,7 +15315,7 @@
         <v>2024</v>
       </c>
       <c r="D564" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E564">
         <v>3</v>
@@ -15293,7 +15338,7 @@
         <v>2024</v>
       </c>
       <c r="D565" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E565">
         <v>4</v>
@@ -15316,7 +15361,7 @@
         <v>2024</v>
       </c>
       <c r="D566" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E566">
         <v>4</v>
@@ -15339,7 +15384,7 @@
         <v>2024</v>
       </c>
       <c r="D567" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E567">
         <v>2</v>
@@ -15362,7 +15407,7 @@
         <v>2024</v>
       </c>
       <c r="D568" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E568">
         <v>3</v>
@@ -15385,7 +15430,7 @@
         <v>2024</v>
       </c>
       <c r="D569" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E569">
         <v>4</v>
@@ -15408,7 +15453,7 @@
         <v>2024</v>
       </c>
       <c r="D570" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E570">
         <v>1</v>
@@ -15431,7 +15476,7 @@
         <v>2024</v>
       </c>
       <c r="D571" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E571">
         <v>4</v>
@@ -15454,7 +15499,7 @@
         <v>2024</v>
       </c>
       <c r="D572" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E572">
         <v>1</v>
@@ -15477,7 +15522,7 @@
         <v>2024</v>
       </c>
       <c r="D573" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E573">
         <v>1</v>
@@ -15500,7 +15545,7 @@
         <v>2024</v>
       </c>
       <c r="D574" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E574">
         <v>4</v>
@@ -15523,7 +15568,7 @@
         <v>2024</v>
       </c>
       <c r="D575" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E575">
         <v>2</v>
@@ -15546,7 +15591,7 @@
         <v>2024</v>
       </c>
       <c r="D576" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E576">
         <v>2</v>
@@ -15569,7 +15614,7 @@
         <v>2024</v>
       </c>
       <c r="D577" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E577">
         <v>4</v>
@@ -15592,7 +15637,7 @@
         <v>2024</v>
       </c>
       <c r="D578" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E578">
         <v>2</v>
@@ -15615,7 +15660,7 @@
         <v>2024</v>
       </c>
       <c r="D579" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E579">
         <v>3</v>
@@ -15638,7 +15683,7 @@
         <v>2024</v>
       </c>
       <c r="D580" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E580">
         <v>2</v>
@@ -15661,7 +15706,7 @@
         <v>2024</v>
       </c>
       <c r="D581" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E581">
         <v>2</v>
@@ -15684,7 +15729,7 @@
         <v>2024</v>
       </c>
       <c r="D582" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E582">
         <v>6</v>
@@ -15719,7 +15764,7 @@
         <v>2024</v>
       </c>
       <c r="D583" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E583">
         <v>1</v>
@@ -15742,7 +15787,7 @@
         <v>2024</v>
       </c>
       <c r="D584" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E584">
         <v>4</v>
@@ -15765,7 +15810,7 @@
         <v>2024</v>
       </c>
       <c r="D585" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E585">
         <v>3</v>
@@ -15788,7 +15833,7 @@
         <v>2024</v>
       </c>
       <c r="D586" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E586">
         <v>3</v>
@@ -15811,7 +15856,7 @@
         <v>2024</v>
       </c>
       <c r="D587" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E587">
         <v>4</v>
@@ -15834,7 +15879,7 @@
         <v>2024</v>
       </c>
       <c r="D588" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E588">
         <v>3</v>
@@ -15857,7 +15902,7 @@
         <v>2024</v>
       </c>
       <c r="D589" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E589">
         <v>2</v>
@@ -15880,7 +15925,7 @@
         <v>2024</v>
       </c>
       <c r="D590" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E590">
         <v>4</v>
@@ -15903,7 +15948,7 @@
         <v>2024</v>
       </c>
       <c r="D591" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E591">
         <v>4</v>
@@ -15926,7 +15971,7 @@
         <v>2024</v>
       </c>
       <c r="D592" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E592">
         <v>3</v>
@@ -15955,7 +16000,7 @@
         <v>2024</v>
       </c>
       <c r="D593" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E593">
         <v>4</v>
@@ -15978,7 +16023,7 @@
         <v>2024</v>
       </c>
       <c r="D594" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E594">
         <v>4</v>
@@ -16001,7 +16046,7 @@
         <v>2024</v>
       </c>
       <c r="D595" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E595">
         <v>1</v>
@@ -16024,7 +16069,7 @@
         <v>2024</v>
       </c>
       <c r="D596" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E596">
         <v>4</v>
@@ -16047,7 +16092,7 @@
         <v>2024</v>
       </c>
       <c r="D597" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E597">
         <v>3</v>
@@ -16070,7 +16115,7 @@
         <v>2024</v>
       </c>
       <c r="D598" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E598">
         <v>3</v>
@@ -16093,7 +16138,7 @@
         <v>2024</v>
       </c>
       <c r="D599" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E599">
         <v>4</v>
@@ -16116,7 +16161,7 @@
         <v>2024</v>
       </c>
       <c r="D600" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E600">
         <v>3</v>
@@ -16139,7 +16184,7 @@
         <v>2024</v>
       </c>
       <c r="D601" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E601">
         <v>1</v>
@@ -16162,7 +16207,7 @@
         <v>2024</v>
       </c>
       <c r="D602" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E602">
         <v>2</v>
@@ -16185,7 +16230,7 @@
         <v>2024</v>
       </c>
       <c r="D603" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E603">
         <v>4</v>
@@ -16208,7 +16253,7 @@
         <v>2024</v>
       </c>
       <c r="D604" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E604">
         <v>4</v>
@@ -16231,7 +16276,7 @@
         <v>2024</v>
       </c>
       <c r="D605" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E605">
         <v>4</v>
@@ -16254,7 +16299,7 @@
         <v>2024</v>
       </c>
       <c r="D606" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E606">
         <v>4</v>
@@ -16277,7 +16322,7 @@
         <v>2024</v>
       </c>
       <c r="D607" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E607">
         <v>3</v>
@@ -16300,7 +16345,7 @@
         <v>2024</v>
       </c>
       <c r="D608" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E608">
         <v>1</v>
@@ -16323,7 +16368,7 @@
         <v>2024</v>
       </c>
       <c r="D609" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E609">
         <v>2</v>
@@ -16346,7 +16391,7 @@
         <v>2024</v>
       </c>
       <c r="D610" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E610">
         <v>4</v>
@@ -16369,7 +16414,7 @@
         <v>2024</v>
       </c>
       <c r="D611" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E611">
         <v>3</v>
@@ -16392,7 +16437,7 @@
         <v>2024</v>
       </c>
       <c r="D612" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E612">
         <v>3</v>
@@ -16415,7 +16460,7 @@
         <v>2024</v>
       </c>
       <c r="D613" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E613">
         <v>3</v>
@@ -16438,7 +16483,7 @@
         <v>2024</v>
       </c>
       <c r="D614" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E614">
         <v>1</v>
@@ -16461,7 +16506,7 @@
         <v>2024</v>
       </c>
       <c r="D615" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E615">
         <v>4</v>
@@ -16484,7 +16529,7 @@
         <v>2024</v>
       </c>
       <c r="D616" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E616">
         <v>1</v>
@@ -16507,7 +16552,7 @@
         <v>2024</v>
       </c>
       <c r="D617" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E617">
         <v>1</v>
@@ -16530,7 +16575,7 @@
         <v>2024</v>
       </c>
       <c r="D618" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E618">
         <v>3</v>
@@ -16553,7 +16598,7 @@
         <v>2024</v>
       </c>
       <c r="D619" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E619">
         <v>3</v>
@@ -16576,7 +16621,7 @@
         <v>2024</v>
       </c>
       <c r="D620" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E620">
         <v>4</v>
@@ -16599,7 +16644,7 @@
         <v>2024</v>
       </c>
       <c r="D621" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E621">
         <v>3</v>
@@ -16622,7 +16667,7 @@
         <v>2024</v>
       </c>
       <c r="D622" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E622">
         <v>3</v>
@@ -16645,7 +16690,7 @@
         <v>2024</v>
       </c>
       <c r="D623" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E623">
         <v>3</v>
@@ -16668,7 +16713,7 @@
         <v>2024</v>
       </c>
       <c r="D624" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E624">
         <v>4</v>
@@ -16691,7 +16736,7 @@
         <v>2024</v>
       </c>
       <c r="D625" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E625">
         <v>4</v>
@@ -16714,7 +16759,7 @@
         <v>2024</v>
       </c>
       <c r="D626" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E626">
         <v>7</v>
@@ -16746,7 +16791,7 @@
         <v>2024</v>
       </c>
       <c r="D627" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E627">
         <v>3</v>
@@ -16769,7 +16814,7 @@
         <v>2024</v>
       </c>
       <c r="D628" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E628">
         <v>1</v>
@@ -16792,7 +16837,7 @@
         <v>2024</v>
       </c>
       <c r="D629" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E629">
         <v>1</v>
@@ -16815,7 +16860,7 @@
         <v>2024</v>
       </c>
       <c r="D630" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E630">
         <v>2</v>
@@ -16838,7 +16883,7 @@
         <v>2024</v>
       </c>
       <c r="D631" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E631">
         <v>3</v>
@@ -16861,7 +16906,7 @@
         <v>2024</v>
       </c>
       <c r="D632" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E632">
         <v>3</v>
@@ -16884,7 +16929,7 @@
         <v>2024</v>
       </c>
       <c r="D633" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E633">
         <v>3</v>
@@ -16907,7 +16952,7 @@
         <v>2024</v>
       </c>
       <c r="D634" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E634">
         <v>4</v>
@@ -16930,7 +16975,7 @@
         <v>2024</v>
       </c>
       <c r="D635" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E635">
         <v>1</v>
@@ -16953,7 +16998,7 @@
         <v>2024</v>
       </c>
       <c r="D636" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E636">
         <v>4</v>
@@ -16976,7 +17021,7 @@
         <v>2024</v>
       </c>
       <c r="D637" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E637">
         <v>3</v>
@@ -16999,7 +17044,7 @@
         <v>2024</v>
       </c>
       <c r="D638" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E638">
         <v>3</v>
@@ -17022,7 +17067,7 @@
         <v>2024</v>
       </c>
       <c r="D639" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E639">
         <v>4</v>
@@ -17045,7 +17090,7 @@
         <v>2024</v>
       </c>
       <c r="D640" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E640">
         <v>3</v>
@@ -17068,7 +17113,7 @@
         <v>2024</v>
       </c>
       <c r="D641" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E641">
         <v>1</v>
@@ -17091,7 +17136,7 @@
         <v>2024</v>
       </c>
       <c r="D642" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E642">
         <v>1</v>
@@ -17114,7 +17159,7 @@
         <v>2024</v>
       </c>
       <c r="D643" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E643">
         <v>1</v>
@@ -17143,7 +17188,7 @@
         <v>2024</v>
       </c>
       <c r="D644" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E644">
         <v>7</v>
@@ -17178,7 +17223,7 @@
         <v>2024</v>
       </c>
       <c r="D645" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E645">
         <v>2</v>
@@ -17201,7 +17246,7 @@
         <v>2024</v>
       </c>
       <c r="D646" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E646">
         <v>4</v>
@@ -17230,7 +17275,7 @@
         <v>2024</v>
       </c>
       <c r="D647" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E647">
         <v>3</v>
@@ -17259,7 +17304,7 @@
         <v>2024</v>
       </c>
       <c r="D648" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E648">
         <v>4</v>
@@ -17282,7 +17327,7 @@
         <v>2024</v>
       </c>
       <c r="D649" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E649">
         <v>3</v>
@@ -17305,7 +17350,7 @@
         <v>2024</v>
       </c>
       <c r="D650" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E650">
         <v>3</v>
@@ -17328,7 +17373,7 @@
         <v>2024</v>
       </c>
       <c r="D651" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E651">
         <v>1</v>
@@ -17351,7 +17396,7 @@
         <v>2024</v>
       </c>
       <c r="D652" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E652">
         <v>2</v>
@@ -17374,7 +17419,7 @@
         <v>2024</v>
       </c>
       <c r="D653" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E653">
         <v>4</v>
@@ -17397,7 +17442,7 @@
         <v>2024</v>
       </c>
       <c r="D654" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E654">
         <v>2</v>
@@ -17420,7 +17465,7 @@
         <v>2024</v>
       </c>
       <c r="D655" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E655">
         <v>4</v>
@@ -17443,7 +17488,7 @@
         <v>2024</v>
       </c>
       <c r="D656" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E656">
         <v>3</v>
@@ -17466,7 +17511,7 @@
         <v>2024</v>
       </c>
       <c r="D657" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E657">
         <v>2</v>
@@ -17489,7 +17534,7 @@
         <v>2024</v>
       </c>
       <c r="D658" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E658">
         <v>3</v>
@@ -17512,7 +17557,7 @@
         <v>2024</v>
       </c>
       <c r="D659" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E659">
         <v>5</v>
@@ -17547,7 +17592,7 @@
         <v>2024</v>
       </c>
       <c r="D660" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E660">
         <v>4</v>
@@ -17570,7 +17615,7 @@
         <v>2024</v>
       </c>
       <c r="D661" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E661">
         <v>3</v>
@@ -17593,7 +17638,7 @@
         <v>2024</v>
       </c>
       <c r="D662" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E662">
         <v>4</v>
@@ -17616,7 +17661,7 @@
         <v>2024</v>
       </c>
       <c r="D663" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E663">
         <v>2</v>
@@ -17639,7 +17684,7 @@
         <v>2024</v>
       </c>
       <c r="D664" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E664">
         <v>3</v>
@@ -17662,7 +17707,7 @@
         <v>2024</v>
       </c>
       <c r="D665" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E665">
         <v>4</v>
@@ -17685,7 +17730,7 @@
         <v>2024</v>
       </c>
       <c r="D666" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E666">
         <v>3</v>
@@ -17708,7 +17753,7 @@
         <v>2024</v>
       </c>
       <c r="D667" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E667">
         <v>4</v>
@@ -17731,7 +17776,7 @@
         <v>2024</v>
       </c>
       <c r="D668" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E668">
         <v>1</v>
@@ -17754,7 +17799,7 @@
         <v>2025</v>
       </c>
       <c r="D669" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E669">
         <v>4</v>
@@ -17777,7 +17822,7 @@
         <v>2025</v>
       </c>
       <c r="D670" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E670">
         <v>2</v>
@@ -17800,7 +17845,7 @@
         <v>2025</v>
       </c>
       <c r="D671" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E671">
         <v>3</v>
@@ -17823,7 +17868,7 @@
         <v>2025</v>
       </c>
       <c r="D672" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E672">
         <v>1</v>
@@ -17846,7 +17891,7 @@
         <v>2025</v>
       </c>
       <c r="D673" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E673">
         <v>3</v>
@@ -17869,7 +17914,7 @@
         <v>2025</v>
       </c>
       <c r="D674" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E674">
         <v>1</v>
@@ -17892,7 +17937,7 @@
         <v>2025</v>
       </c>
       <c r="D675" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E675">
         <v>1</v>
@@ -17915,7 +17960,7 @@
         <v>2025</v>
       </c>
       <c r="D676" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E676">
         <v>4</v>
@@ -17938,7 +17983,7 @@
         <v>2025</v>
       </c>
       <c r="D677" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E677">
         <v>1</v>
@@ -17961,7 +18006,7 @@
         <v>2025</v>
       </c>
       <c r="D678" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E678">
         <v>3</v>
@@ -17984,7 +18029,7 @@
         <v>2025</v>
       </c>
       <c r="D679" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E679">
         <v>4</v>
@@ -18007,7 +18052,7 @@
         <v>2025</v>
       </c>
       <c r="D680" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E680">
         <v>2</v>
@@ -18030,7 +18075,7 @@
         <v>2025</v>
       </c>
       <c r="D681" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E681">
         <v>4</v>
@@ -18053,7 +18098,7 @@
         <v>2025</v>
       </c>
       <c r="D682" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E682">
         <v>1</v>
@@ -18076,7 +18121,7 @@
         <v>2025</v>
       </c>
       <c r="D683" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E683">
         <v>3</v>
@@ -18099,7 +18144,7 @@
         <v>2025</v>
       </c>
       <c r="D684" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E684">
         <v>3</v>
@@ -18122,7 +18167,7 @@
         <v>2025</v>
       </c>
       <c r="D685" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E685">
         <v>4</v>
@@ -18151,7 +18196,7 @@
         <v>2025</v>
       </c>
       <c r="D686" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E686">
         <v>2</v>
@@ -18174,7 +18219,7 @@
         <v>2025</v>
       </c>
       <c r="D687" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E687">
         <v>3</v>
@@ -18197,7 +18242,7 @@
         <v>2025</v>
       </c>
       <c r="D688" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E688">
         <v>3</v>
@@ -18217,7 +18262,7 @@
         <v>2025</v>
       </c>
       <c r="D689" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E689">
         <v>3</v>
@@ -18240,7 +18285,7 @@
         <v>2025</v>
       </c>
       <c r="D690" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E690">
         <v>4</v>
@@ -18263,7 +18308,7 @@
         <v>2025</v>
       </c>
       <c r="D691" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E691">
         <v>3</v>
@@ -18286,7 +18331,7 @@
         <v>2025</v>
       </c>
       <c r="D692" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E692">
         <v>4</v>
@@ -18309,7 +18354,7 @@
         <v>2025</v>
       </c>
       <c r="D693" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E693">
         <v>2</v>
@@ -18332,7 +18377,7 @@
         <v>2025</v>
       </c>
       <c r="D694" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E694">
         <v>4</v>
@@ -18355,7 +18400,7 @@
         <v>2025</v>
       </c>
       <c r="D695" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E695">
         <v>4</v>
@@ -18378,7 +18423,7 @@
         <v>2025</v>
       </c>
       <c r="D696" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E696">
         <v>3</v>
@@ -18401,7 +18446,7 @@
         <v>2025</v>
       </c>
       <c r="D697" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E697">
         <v>3</v>
@@ -18424,7 +18469,7 @@
         <v>2025</v>
       </c>
       <c r="D698" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E698">
         <v>1</v>
@@ -18447,7 +18492,7 @@
         <v>2025</v>
       </c>
       <c r="D699" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E699">
         <v>4</v>
@@ -18476,7 +18521,7 @@
         <v>2025</v>
       </c>
       <c r="D700" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E700">
         <v>3</v>
@@ -18499,7 +18544,7 @@
         <v>2025</v>
       </c>
       <c r="D701" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E701">
         <v>1</v>
@@ -18522,7 +18567,7 @@
         <v>2025</v>
       </c>
       <c r="D702" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E702">
         <v>4</v>
@@ -18545,7 +18590,7 @@
         <v>2025</v>
       </c>
       <c r="D703" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E703">
         <v>4</v>
@@ -18568,7 +18613,7 @@
         <v>2025</v>
       </c>
       <c r="D704" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E704">
         <v>3</v>
@@ -18591,7 +18636,7 @@
         <v>2025</v>
       </c>
       <c r="D705" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E705">
         <v>4</v>
@@ -18614,7 +18659,7 @@
         <v>2025</v>
       </c>
       <c r="D706" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E706">
         <v>4</v>
@@ -18637,7 +18682,7 @@
         <v>2025</v>
       </c>
       <c r="D707" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E707">
         <v>3</v>
@@ -18660,7 +18705,7 @@
         <v>2025</v>
       </c>
       <c r="D708" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E708">
         <v>2</v>
@@ -18683,7 +18728,7 @@
         <v>2025</v>
       </c>
       <c r="D709" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E709">
         <v>6</v>
@@ -18718,7 +18763,7 @@
         <v>2025</v>
       </c>
       <c r="D710" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E710">
         <v>2</v>
@@ -18741,7 +18786,7 @@
         <v>2025</v>
       </c>
       <c r="D711" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E711">
         <v>1</v>
@@ -18764,7 +18809,7 @@
         <v>2025</v>
       </c>
       <c r="D712" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E712">
         <v>1</v>
@@ -18787,7 +18832,7 @@
         <v>2025</v>
       </c>
       <c r="D713" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E713">
         <v>4</v>
@@ -18810,7 +18855,7 @@
         <v>2025</v>
       </c>
       <c r="D714" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E714">
         <v>2</v>
@@ -18833,7 +18878,7 @@
         <v>2025</v>
       </c>
       <c r="D715" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E715">
         <v>4</v>
@@ -18856,7 +18901,7 @@
         <v>2025</v>
       </c>
       <c r="D716" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E716">
         <v>2</v>
@@ -18879,7 +18924,7 @@
         <v>2025</v>
       </c>
       <c r="D717" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E717">
         <v>1</v>
@@ -18902,7 +18947,7 @@
         <v>2025</v>
       </c>
       <c r="D718" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E718">
         <v>2</v>
@@ -18925,7 +18970,7 @@
         <v>2025</v>
       </c>
       <c r="D719" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E719">
         <v>4</v>
@@ -18948,7 +18993,7 @@
         <v>2025</v>
       </c>
       <c r="D720" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E720">
         <v>3</v>
@@ -18971,7 +19016,7 @@
         <v>2025</v>
       </c>
       <c r="D721" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E721">
         <v>1</v>
@@ -18994,7 +19039,7 @@
         <v>2025</v>
       </c>
       <c r="D722" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E722">
         <v>2</v>
@@ -19017,7 +19062,7 @@
         <v>2025</v>
       </c>
       <c r="D723" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E723">
         <v>2</v>
@@ -19040,7 +19085,7 @@
         <v>2025</v>
       </c>
       <c r="D724" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E724">
         <v>2</v>
@@ -19063,7 +19108,7 @@
         <v>2025</v>
       </c>
       <c r="D725" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E725">
         <v>4</v>
@@ -19086,7 +19131,7 @@
         <v>2025</v>
       </c>
       <c r="D726" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E726">
         <v>4</v>
@@ -19109,7 +19154,7 @@
         <v>2025</v>
       </c>
       <c r="D727" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E727">
         <v>2</v>
@@ -19132,7 +19177,7 @@
         <v>2025</v>
       </c>
       <c r="D728" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E728">
         <v>3</v>
@@ -19155,7 +19200,7 @@
         <v>2025</v>
       </c>
       <c r="D729" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E729">
         <v>4</v>
@@ -19178,7 +19223,7 @@
         <v>2025</v>
       </c>
       <c r="D730" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E730">
         <v>3</v>
@@ -19201,7 +19246,7 @@
         <v>2025</v>
       </c>
       <c r="D731" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E731">
         <v>2</v>
@@ -19224,7 +19269,7 @@
         <v>2025</v>
       </c>
       <c r="D732" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E732">
         <v>4</v>
@@ -19247,7 +19292,7 @@
         <v>2025</v>
       </c>
       <c r="D733" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E733">
         <v>2</v>
@@ -19270,7 +19315,7 @@
         <v>2025</v>
       </c>
       <c r="D734" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E734">
         <v>2</v>
@@ -19293,7 +19338,7 @@
         <v>2025</v>
       </c>
       <c r="D735" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E735">
         <v>4</v>
@@ -19316,7 +19361,7 @@
         <v>2025</v>
       </c>
       <c r="D736" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E736">
         <v>4</v>
@@ -19339,7 +19384,7 @@
         <v>2025</v>
       </c>
       <c r="D737" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E737">
         <v>4</v>
@@ -19362,7 +19407,7 @@
         <v>2025</v>
       </c>
       <c r="D738" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E738">
         <v>3</v>
@@ -19385,7 +19430,7 @@
         <v>2025</v>
       </c>
       <c r="D739" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E739">
         <v>3</v>
@@ -19408,7 +19453,7 @@
         <v>2025</v>
       </c>
       <c r="D740" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E740">
         <v>4</v>
@@ -19431,7 +19476,7 @@
         <v>2025</v>
       </c>
       <c r="D741" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E741">
         <v>2</v>
@@ -19454,7 +19499,7 @@
         <v>2025</v>
       </c>
       <c r="D742" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="E742">
         <v>13</v>
@@ -19489,7 +19534,7 @@
         <v>2025</v>
       </c>
       <c r="D743" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E743">
         <v>3</v>
@@ -19512,7 +19557,7 @@
         <v>2025</v>
       </c>
       <c r="D744" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E744">
         <v>4</v>
@@ -19535,7 +19580,7 @@
         <v>2025</v>
       </c>
       <c r="D745" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E745">
         <v>3</v>
@@ -19558,7 +19603,7 @@
         <v>2025</v>
       </c>
       <c r="D746" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E746">
         <v>1</v>
@@ -19581,7 +19626,7 @@
         <v>2025</v>
       </c>
       <c r="D747" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="E747">
         <v>4</v>
@@ -19616,7 +19661,7 @@
         <v>2025</v>
       </c>
       <c r="D748" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E748">
         <v>4</v>
@@ -19639,7 +19684,7 @@
         <v>2025</v>
       </c>
       <c r="D749" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E749">
         <v>2</v>
@@ -19662,7 +19707,7 @@
         <v>2025</v>
       </c>
       <c r="D750" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E750">
         <v>1</v>
@@ -19691,7 +19736,7 @@
         <v>2025</v>
       </c>
       <c r="D751" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E751">
         <v>2</v>
@@ -19714,7 +19759,7 @@
         <v>2025</v>
       </c>
       <c r="D752" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E752">
         <v>1</v>
@@ -19737,7 +19782,7 @@
         <v>2025</v>
       </c>
       <c r="D753" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E753">
         <v>4</v>
@@ -19760,7 +19805,7 @@
         <v>2025</v>
       </c>
       <c r="D754" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E754">
         <v>1</v>
@@ -19783,7 +19828,7 @@
         <v>2025</v>
       </c>
       <c r="D755" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E755">
         <v>4</v>
@@ -19812,7 +19857,7 @@
         <v>2025</v>
       </c>
       <c r="D756" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E756">
         <v>1</v>
@@ -19835,7 +19880,7 @@
         <v>2025</v>
       </c>
       <c r="D757" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E757">
         <v>2</v>
@@ -19858,7 +19903,7 @@
         <v>2025</v>
       </c>
       <c r="D758" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="E758">
         <v>4</v>
@@ -19887,7 +19932,7 @@
         <v>2025</v>
       </c>
       <c r="D759" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E759">
         <v>3</v>
@@ -19910,7 +19955,7 @@
         <v>2025</v>
       </c>
       <c r="D760" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E760">
         <v>3</v>
@@ -19933,7 +19978,7 @@
         <v>2025</v>
       </c>
       <c r="D761" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E761">
         <v>3</v>
@@ -19956,7 +20001,7 @@
         <v>2025</v>
       </c>
       <c r="D762" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E762">
         <v>3</v>
@@ -19979,7 +20024,7 @@
         <v>2025</v>
       </c>
       <c r="D763" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E763">
         <v>4</v>
@@ -20002,7 +20047,7 @@
         <v>2025</v>
       </c>
       <c r="D764" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E764">
         <v>3</v>
@@ -20025,7 +20070,7 @@
         <v>2025</v>
       </c>
       <c r="D765" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E765">
         <v>3</v>
@@ -20048,7 +20093,7 @@
         <v>2025</v>
       </c>
       <c r="D766" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E766">
         <v>4</v>
@@ -20071,7 +20116,7 @@
         <v>2025</v>
       </c>
       <c r="D767" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E767">
         <v>4</v>
@@ -20094,7 +20139,7 @@
         <v>2025</v>
       </c>
       <c r="D768" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E768">
         <v>4</v>
@@ -20117,7 +20162,7 @@
         <v>2025</v>
       </c>
       <c r="D769" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E769">
         <v>1</v>
@@ -20140,7 +20185,7 @@
         <v>2025</v>
       </c>
       <c r="D770" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E770">
         <v>3</v>
@@ -20163,7 +20208,7 @@
         <v>2025</v>
       </c>
       <c r="D771" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E771">
         <v>4</v>
@@ -20186,7 +20231,7 @@
         <v>2025</v>
       </c>
       <c r="D772" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E772">
         <v>4</v>
@@ -20209,7 +20254,7 @@
         <v>2025</v>
       </c>
       <c r="D773" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E773">
         <v>4</v>
@@ -20232,7 +20277,7 @@
         <v>2025</v>
       </c>
       <c r="D774" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="E774">
         <v>3</v>
@@ -20255,16 +20300,2387 @@
         <v>2025</v>
       </c>
       <c r="D775" t="s">
+        <v>518</v>
+      </c>
+      <c r="E775">
+        <v>4</v>
+      </c>
+      <c r="H775">
+        <v>4</v>
+      </c>
+      <c r="K775">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="776" spans="1:11">
+      <c r="A776">
+        <v>24396</v>
+      </c>
+      <c r="B776" t="s">
+        <v>57</v>
+      </c>
+      <c r="C776">
+        <v>2026</v>
+      </c>
+      <c r="D776" t="s">
+        <v>518</v>
+      </c>
+      <c r="E776">
+        <v>1</v>
+      </c>
+      <c r="H776">
+        <v>1</v>
+      </c>
+      <c r="K776">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="777" spans="1:11">
+      <c r="A777">
+        <v>7966</v>
+      </c>
+      <c r="B777" t="s">
+        <v>56</v>
+      </c>
+      <c r="C777">
+        <v>2026</v>
+      </c>
+      <c r="D777" t="s">
+        <v>518</v>
+      </c>
+      <c r="E777">
+        <v>2</v>
+      </c>
+      <c r="H777">
+        <v>2</v>
+      </c>
+      <c r="K777">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="778" spans="1:11">
+      <c r="A778">
+        <v>12051</v>
+      </c>
+      <c r="B778" t="s">
+        <v>58</v>
+      </c>
+      <c r="C778">
+        <v>2026</v>
+      </c>
+      <c r="D778" t="s">
+        <v>518</v>
+      </c>
+      <c r="E778">
+        <v>3</v>
+      </c>
+      <c r="H778">
+        <v>3</v>
+      </c>
+      <c r="K778">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="779" spans="1:11">
+      <c r="A779">
+        <v>23609</v>
+      </c>
+      <c r="B779" t="s">
+        <v>62</v>
+      </c>
+      <c r="C779">
+        <v>2026</v>
+      </c>
+      <c r="D779" t="s">
+        <v>518</v>
+      </c>
+      <c r="E779">
+        <v>4</v>
+      </c>
+      <c r="H779">
+        <v>4</v>
+      </c>
+      <c r="K779">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="780" spans="1:11">
+      <c r="A780">
+        <v>83502</v>
+      </c>
+      <c r="B780" t="s">
         <v>503</v>
       </c>
-      <c r="E775">
-        <v>4</v>
-      </c>
-      <c r="H775">
-        <v>4</v>
-      </c>
-      <c r="K775">
-        <v>4</v>
+      <c r="C780">
+        <v>2026</v>
+      </c>
+      <c r="D780" t="s">
+        <v>518</v>
+      </c>
+      <c r="E780">
+        <v>4</v>
+      </c>
+      <c r="H780">
+        <v>4</v>
+      </c>
+      <c r="K780">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="781" spans="1:11">
+      <c r="A781">
+        <v>263530</v>
+      </c>
+      <c r="B781" t="s">
+        <v>64</v>
+      </c>
+      <c r="C781">
+        <v>2026</v>
+      </c>
+      <c r="D781" t="s">
+        <v>520</v>
+      </c>
+      <c r="E781">
+        <v>9</v>
+      </c>
+      <c r="F781">
+        <v>29</v>
+      </c>
+      <c r="G781">
+        <v>29.11111111111111</v>
+      </c>
+      <c r="H781">
+        <v>9</v>
+      </c>
+      <c r="I781">
+        <v>17</v>
+      </c>
+      <c r="J781">
+        <v>16.66666666666667</v>
+      </c>
+      <c r="K781">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="782" spans="1:11">
+      <c r="A782">
+        <v>263535</v>
+      </c>
+      <c r="B782" t="s">
+        <v>65</v>
+      </c>
+      <c r="C782">
+        <v>2026</v>
+      </c>
+      <c r="D782" t="s">
+        <v>518</v>
+      </c>
+      <c r="E782">
+        <v>2</v>
+      </c>
+      <c r="H782">
+        <v>2</v>
+      </c>
+      <c r="K782">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="783" spans="1:11">
+      <c r="A783">
+        <v>27553</v>
+      </c>
+      <c r="B783" t="s">
+        <v>66</v>
+      </c>
+      <c r="C783">
+        <v>2026</v>
+      </c>
+      <c r="D783" t="s">
+        <v>518</v>
+      </c>
+      <c r="E783">
+        <v>3</v>
+      </c>
+      <c r="H783">
+        <v>3</v>
+      </c>
+      <c r="K783">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="784" spans="1:11">
+      <c r="A784">
+        <v>74367</v>
+      </c>
+      <c r="B784" t="s">
+        <v>67</v>
+      </c>
+      <c r="C784">
+        <v>2026</v>
+      </c>
+      <c r="D784" t="s">
+        <v>518</v>
+      </c>
+      <c r="E784">
+        <v>2</v>
+      </c>
+      <c r="H784">
+        <v>2</v>
+      </c>
+      <c r="K784">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="785" spans="1:11">
+      <c r="A785">
+        <v>50844</v>
+      </c>
+      <c r="B785" t="s">
+        <v>70</v>
+      </c>
+      <c r="C785">
+        <v>2026</v>
+      </c>
+      <c r="D785" t="s">
+        <v>518</v>
+      </c>
+      <c r="E785">
+        <v>3</v>
+      </c>
+      <c r="H785">
+        <v>3</v>
+      </c>
+      <c r="K785">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="786" spans="1:11">
+      <c r="A786">
+        <v>83315</v>
+      </c>
+      <c r="B786" t="s">
+        <v>399</v>
+      </c>
+      <c r="C786">
+        <v>2026</v>
+      </c>
+      <c r="D786" t="s">
+        <v>518</v>
+      </c>
+      <c r="E786">
+        <v>4</v>
+      </c>
+      <c r="H786">
+        <v>4</v>
+      </c>
+      <c r="K786">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="787" spans="1:11">
+      <c r="A787">
+        <v>83954</v>
+      </c>
+      <c r="B787" t="s">
+        <v>94</v>
+      </c>
+      <c r="C787">
+        <v>2026</v>
+      </c>
+      <c r="D787" t="s">
+        <v>518</v>
+      </c>
+      <c r="E787">
+        <v>4</v>
+      </c>
+      <c r="H787">
+        <v>4</v>
+      </c>
+      <c r="K787">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="788" spans="1:11">
+      <c r="A788">
+        <v>66473</v>
+      </c>
+      <c r="B788" t="s">
+        <v>98</v>
+      </c>
+      <c r="C788">
+        <v>2026</v>
+      </c>
+      <c r="D788" t="s">
+        <v>518</v>
+      </c>
+      <c r="E788">
+        <v>1</v>
+      </c>
+      <c r="H788">
+        <v>1</v>
+      </c>
+      <c r="K788">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="789" spans="1:11">
+      <c r="A789">
+        <v>47665</v>
+      </c>
+      <c r="B789" t="s">
+        <v>102</v>
+      </c>
+      <c r="C789">
+        <v>2026</v>
+      </c>
+      <c r="D789" t="s">
+        <v>518</v>
+      </c>
+      <c r="E789">
+        <v>1</v>
+      </c>
+      <c r="H789">
+        <v>1</v>
+      </c>
+      <c r="K789">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="790" spans="1:11">
+      <c r="A790">
+        <v>55921</v>
+      </c>
+      <c r="B790" t="s">
+        <v>504</v>
+      </c>
+      <c r="C790">
+        <v>2026</v>
+      </c>
+      <c r="D790" t="s">
+        <v>518</v>
+      </c>
+      <c r="E790">
+        <v>4</v>
+      </c>
+      <c r="H790">
+        <v>4</v>
+      </c>
+      <c r="K790">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="791" spans="1:11">
+      <c r="A791">
+        <v>24340</v>
+      </c>
+      <c r="B791" t="s">
+        <v>107</v>
+      </c>
+      <c r="C791">
+        <v>2026</v>
+      </c>
+      <c r="D791" t="s">
+        <v>518</v>
+      </c>
+      <c r="E791">
+        <v>3</v>
+      </c>
+      <c r="H791">
+        <v>3</v>
+      </c>
+      <c r="K791">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="792" spans="1:11">
+      <c r="A792">
+        <v>24642</v>
+      </c>
+      <c r="B792" t="s">
+        <v>505</v>
+      </c>
+      <c r="C792">
+        <v>2026</v>
+      </c>
+      <c r="D792" t="s">
+        <v>518</v>
+      </c>
+      <c r="E792">
+        <v>4</v>
+      </c>
+      <c r="H792">
+        <v>4</v>
+      </c>
+      <c r="K792">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="793" spans="1:11">
+      <c r="A793">
+        <v>62361</v>
+      </c>
+      <c r="B793" t="s">
+        <v>119</v>
+      </c>
+      <c r="C793">
+        <v>2026</v>
+      </c>
+      <c r="D793" t="s">
+        <v>518</v>
+      </c>
+      <c r="E793">
+        <v>2</v>
+      </c>
+      <c r="H793">
+        <v>2</v>
+      </c>
+      <c r="K793">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="794" spans="1:11">
+      <c r="A794">
+        <v>5896</v>
+      </c>
+      <c r="B794" t="s">
+        <v>121</v>
+      </c>
+      <c r="C794">
+        <v>2026</v>
+      </c>
+      <c r="D794" t="s">
+        <v>518</v>
+      </c>
+      <c r="E794">
+        <v>1</v>
+      </c>
+      <c r="H794">
+        <v>1</v>
+      </c>
+      <c r="K794">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="795" spans="1:11">
+      <c r="A795">
+        <v>5897</v>
+      </c>
+      <c r="B795" t="s">
+        <v>122</v>
+      </c>
+      <c r="C795">
+        <v>2026</v>
+      </c>
+      <c r="D795" t="s">
+        <v>520</v>
+      </c>
+      <c r="E795">
+        <v>5</v>
+      </c>
+      <c r="F795">
+        <v>36</v>
+      </c>
+      <c r="G795">
+        <v>30.8</v>
+      </c>
+      <c r="H795">
+        <v>5</v>
+      </c>
+      <c r="I795">
+        <v>20</v>
+      </c>
+      <c r="J795">
+        <v>24.2</v>
+      </c>
+      <c r="K795">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="796" spans="1:11">
+      <c r="A796">
+        <v>17385</v>
+      </c>
+      <c r="B796" t="s">
+        <v>126</v>
+      </c>
+      <c r="C796">
+        <v>2026</v>
+      </c>
+      <c r="D796" t="s">
+        <v>518</v>
+      </c>
+      <c r="E796">
+        <v>2</v>
+      </c>
+      <c r="H796">
+        <v>2</v>
+      </c>
+      <c r="K796">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="797" spans="1:11">
+      <c r="A797">
+        <v>262698</v>
+      </c>
+      <c r="B797" t="s">
+        <v>128</v>
+      </c>
+      <c r="C797">
+        <v>2026</v>
+      </c>
+      <c r="D797" t="s">
+        <v>518</v>
+      </c>
+      <c r="E797">
+        <v>4</v>
+      </c>
+      <c r="H797">
+        <v>4</v>
+      </c>
+      <c r="K797">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="798" spans="1:11">
+      <c r="A798">
+        <v>273797</v>
+      </c>
+      <c r="B798" t="s">
+        <v>131</v>
+      </c>
+      <c r="C798">
+        <v>2026</v>
+      </c>
+      <c r="D798" t="s">
+        <v>518</v>
+      </c>
+      <c r="E798">
+        <v>4</v>
+      </c>
+      <c r="H798">
+        <v>4</v>
+      </c>
+      <c r="K798">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="799" spans="1:11">
+      <c r="A799">
+        <v>75638</v>
+      </c>
+      <c r="B799" t="s">
+        <v>135</v>
+      </c>
+      <c r="C799">
+        <v>2026</v>
+      </c>
+      <c r="D799" t="s">
+        <v>518</v>
+      </c>
+      <c r="E799">
+        <v>2</v>
+      </c>
+      <c r="H799">
+        <v>2</v>
+      </c>
+      <c r="K799">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="800" spans="1:11">
+      <c r="A800">
+        <v>9412</v>
+      </c>
+      <c r="B800" t="s">
+        <v>506</v>
+      </c>
+      <c r="C800">
+        <v>2026</v>
+      </c>
+      <c r="D800" t="s">
+        <v>518</v>
+      </c>
+      <c r="E800">
+        <v>4</v>
+      </c>
+      <c r="H800">
+        <v>4</v>
+      </c>
+      <c r="K800">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="801" spans="1:13">
+      <c r="A801">
+        <v>479294</v>
+      </c>
+      <c r="B801" t="s">
+        <v>486</v>
+      </c>
+      <c r="C801">
+        <v>2026</v>
+      </c>
+      <c r="D801" t="s">
+        <v>518</v>
+      </c>
+      <c r="E801">
+        <v>4</v>
+      </c>
+      <c r="H801">
+        <v>4</v>
+      </c>
+      <c r="K801">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="802" spans="1:13">
+      <c r="A802">
+        <v>123027</v>
+      </c>
+      <c r="B802" t="s">
+        <v>441</v>
+      </c>
+      <c r="C802">
+        <v>2026</v>
+      </c>
+      <c r="D802" t="s">
+        <v>518</v>
+      </c>
+      <c r="E802">
+        <v>4</v>
+      </c>
+      <c r="H802">
+        <v>4</v>
+      </c>
+      <c r="K802">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="803" spans="1:13">
+      <c r="A803">
+        <v>84653</v>
+      </c>
+      <c r="B803" t="s">
+        <v>442</v>
+      </c>
+      <c r="C803">
+        <v>2026</v>
+      </c>
+      <c r="D803" t="s">
+        <v>518</v>
+      </c>
+      <c r="E803">
+        <v>4</v>
+      </c>
+      <c r="H803">
+        <v>4</v>
+      </c>
+      <c r="K803">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="804" spans="1:13">
+      <c r="A804">
+        <v>29737</v>
+      </c>
+      <c r="B804" t="s">
+        <v>507</v>
+      </c>
+      <c r="C804">
+        <v>2026</v>
+      </c>
+      <c r="D804" t="s">
+        <v>518</v>
+      </c>
+      <c r="E804">
+        <v>4</v>
+      </c>
+      <c r="H804">
+        <v>4</v>
+      </c>
+      <c r="K804">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="805" spans="1:13">
+      <c r="A805">
+        <v>3494</v>
+      </c>
+      <c r="B805" t="s">
+        <v>154</v>
+      </c>
+      <c r="C805">
+        <v>2026</v>
+      </c>
+      <c r="D805" t="s">
+        <v>518</v>
+      </c>
+      <c r="E805">
+        <v>4</v>
+      </c>
+      <c r="H805">
+        <v>4</v>
+      </c>
+      <c r="K805">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="806" spans="1:13">
+      <c r="A806">
+        <v>89283</v>
+      </c>
+      <c r="B806" t="s">
+        <v>162</v>
+      </c>
+      <c r="C806">
+        <v>2026</v>
+      </c>
+      <c r="D806" t="s">
+        <v>518</v>
+      </c>
+      <c r="E806">
+        <v>2</v>
+      </c>
+      <c r="H806">
+        <v>2</v>
+      </c>
+      <c r="K806">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="807" spans="1:13">
+      <c r="A807">
+        <v>6639</v>
+      </c>
+      <c r="B807" t="s">
+        <v>446</v>
+      </c>
+      <c r="C807">
+        <v>2026</v>
+      </c>
+      <c r="D807" t="s">
+        <v>518</v>
+      </c>
+      <c r="E807">
+        <v>2</v>
+      </c>
+      <c r="H807">
+        <v>2</v>
+      </c>
+      <c r="K807">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="808" spans="1:13">
+      <c r="A808">
+        <v>11665</v>
+      </c>
+      <c r="B808" t="s">
+        <v>165</v>
+      </c>
+      <c r="C808">
+        <v>2026</v>
+      </c>
+      <c r="D808" t="s">
+        <v>518</v>
+      </c>
+      <c r="E808">
+        <v>4</v>
+      </c>
+      <c r="H808">
+        <v>4</v>
+      </c>
+      <c r="K808">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="809" spans="1:13">
+      <c r="A809">
+        <v>275377</v>
+      </c>
+      <c r="B809" t="s">
+        <v>166</v>
+      </c>
+      <c r="C809">
+        <v>2026</v>
+      </c>
+      <c r="D809" t="s">
+        <v>518</v>
+      </c>
+      <c r="E809">
+        <v>2</v>
+      </c>
+      <c r="H809">
+        <v>2</v>
+      </c>
+      <c r="K809">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="810" spans="1:13">
+      <c r="A810">
+        <v>69827</v>
+      </c>
+      <c r="B810" t="s">
+        <v>167</v>
+      </c>
+      <c r="C810">
+        <v>2026</v>
+      </c>
+      <c r="D810" t="s">
+        <v>518</v>
+      </c>
+      <c r="E810">
+        <v>4</v>
+      </c>
+      <c r="H810">
+        <v>4</v>
+      </c>
+      <c r="K810">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="811" spans="1:13">
+      <c r="A811">
+        <v>91573</v>
+      </c>
+      <c r="B811" t="s">
+        <v>168</v>
+      </c>
+      <c r="C811">
+        <v>2026</v>
+      </c>
+      <c r="D811" t="s">
+        <v>518</v>
+      </c>
+      <c r="E811">
+        <v>2</v>
+      </c>
+      <c r="H811">
+        <v>2</v>
+      </c>
+      <c r="K811">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="812" spans="1:13">
+      <c r="A812">
+        <v>74083</v>
+      </c>
+      <c r="B812" t="s">
+        <v>187</v>
+      </c>
+      <c r="C812">
+        <v>2026</v>
+      </c>
+      <c r="D812" t="s">
+        <v>518</v>
+      </c>
+      <c r="E812">
+        <v>3</v>
+      </c>
+      <c r="H812">
+        <v>3</v>
+      </c>
+      <c r="K812">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="813" spans="1:13">
+      <c r="A813">
+        <v>109090</v>
+      </c>
+      <c r="B813" t="s">
+        <v>508</v>
+      </c>
+      <c r="C813">
+        <v>2026</v>
+      </c>
+      <c r="D813" t="s">
+        <v>518</v>
+      </c>
+      <c r="E813">
+        <v>4</v>
+      </c>
+      <c r="H813">
+        <v>4</v>
+      </c>
+      <c r="K813">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="814" spans="1:13">
+      <c r="A814">
+        <v>119714</v>
+      </c>
+      <c r="B814" t="s">
+        <v>189</v>
+      </c>
+      <c r="C814">
+        <v>2026</v>
+      </c>
+      <c r="D814" t="s">
+        <v>518</v>
+      </c>
+      <c r="E814">
+        <v>2</v>
+      </c>
+      <c r="H814">
+        <v>2</v>
+      </c>
+      <c r="K814">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="815" spans="1:13">
+      <c r="A815">
+        <v>124721</v>
+      </c>
+      <c r="B815" t="s">
+        <v>196</v>
+      </c>
+      <c r="C815">
+        <v>2026</v>
+      </c>
+      <c r="D815" t="s">
+        <v>520</v>
+      </c>
+      <c r="E815">
+        <v>10</v>
+      </c>
+      <c r="F815">
+        <v>11</v>
+      </c>
+      <c r="G815">
+        <v>14.4</v>
+      </c>
+      <c r="H815">
+        <v>10</v>
+      </c>
+      <c r="I815">
+        <v>20</v>
+      </c>
+      <c r="J815">
+        <v>21.2</v>
+      </c>
+      <c r="K815">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="816" spans="1:13">
+      <c r="A816">
+        <v>82564</v>
+      </c>
+      <c r="B816" t="s">
+        <v>452</v>
+      </c>
+      <c r="C816">
+        <v>2026</v>
+      </c>
+      <c r="D816" t="s">
+        <v>519</v>
+      </c>
+      <c r="E816">
+        <v>1</v>
+      </c>
+      <c r="H816">
+        <v>1</v>
+      </c>
+      <c r="K816">
+        <v>8</v>
+      </c>
+      <c r="L816">
+        <v>21</v>
+      </c>
+      <c r="M816">
+        <v>34.25</v>
+      </c>
+    </row>
+    <row r="817" spans="1:13">
+      <c r="A817">
+        <v>480220</v>
+      </c>
+      <c r="B817" t="s">
+        <v>220</v>
+      </c>
+      <c r="C817">
+        <v>2026</v>
+      </c>
+      <c r="D817" t="s">
+        <v>518</v>
+      </c>
+      <c r="E817">
+        <v>2</v>
+      </c>
+      <c r="H817">
+        <v>2</v>
+      </c>
+      <c r="K817">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="818" spans="1:13">
+      <c r="A818">
+        <v>478547</v>
+      </c>
+      <c r="B818" t="s">
+        <v>453</v>
+      </c>
+      <c r="C818">
+        <v>2026</v>
+      </c>
+      <c r="D818" t="s">
+        <v>518</v>
+      </c>
+      <c r="E818">
+        <v>3</v>
+      </c>
+      <c r="H818">
+        <v>3</v>
+      </c>
+      <c r="K818">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="819" spans="1:13">
+      <c r="A819">
+        <v>123896</v>
+      </c>
+      <c r="B819" t="s">
+        <v>214</v>
+      </c>
+      <c r="C819">
+        <v>2026</v>
+      </c>
+      <c r="D819" t="s">
+        <v>519</v>
+      </c>
+      <c r="E819">
+        <v>2</v>
+      </c>
+      <c r="H819">
+        <v>2</v>
+      </c>
+      <c r="K819">
+        <v>5</v>
+      </c>
+      <c r="L819">
+        <v>100</v>
+      </c>
+      <c r="M819">
+        <v>82.40000000000001</v>
+      </c>
+    </row>
+    <row r="820" spans="1:13">
+      <c r="A820">
+        <v>480360</v>
+      </c>
+      <c r="B820" t="s">
+        <v>509</v>
+      </c>
+      <c r="C820">
+        <v>2026</v>
+      </c>
+      <c r="D820" t="s">
+        <v>519</v>
+      </c>
+      <c r="E820">
+        <v>4</v>
+      </c>
+      <c r="H820">
+        <v>4</v>
+      </c>
+      <c r="K820">
+        <v>5</v>
+      </c>
+      <c r="L820">
+        <v>96</v>
+      </c>
+      <c r="M820">
+        <v>82.40000000000001</v>
+      </c>
+    </row>
+    <row r="821" spans="1:13">
+      <c r="A821">
+        <v>30118</v>
+      </c>
+      <c r="B821" t="s">
+        <v>224</v>
+      </c>
+      <c r="C821">
+        <v>2026</v>
+      </c>
+      <c r="D821" t="s">
+        <v>518</v>
+      </c>
+      <c r="E821">
+        <v>4</v>
+      </c>
+      <c r="H821">
+        <v>4</v>
+      </c>
+      <c r="K821">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="822" spans="1:13">
+      <c r="A822">
+        <v>82807</v>
+      </c>
+      <c r="B822" t="s">
+        <v>181</v>
+      </c>
+      <c r="C822">
+        <v>2026</v>
+      </c>
+      <c r="D822" t="s">
+        <v>518</v>
+      </c>
+      <c r="E822">
+        <v>2</v>
+      </c>
+      <c r="H822">
+        <v>2</v>
+      </c>
+      <c r="K822">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="823" spans="1:13">
+      <c r="A823">
+        <v>69076</v>
+      </c>
+      <c r="B823" t="s">
+        <v>229</v>
+      </c>
+      <c r="C823">
+        <v>2026</v>
+      </c>
+      <c r="D823" t="s">
+        <v>518</v>
+      </c>
+      <c r="E823">
+        <v>3</v>
+      </c>
+      <c r="H823">
+        <v>3</v>
+      </c>
+      <c r="K823">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="824" spans="1:13">
+      <c r="A824">
+        <v>91658</v>
+      </c>
+      <c r="B824" t="s">
+        <v>510</v>
+      </c>
+      <c r="C824">
+        <v>2026</v>
+      </c>
+      <c r="D824" t="s">
+        <v>518</v>
+      </c>
+      <c r="E824">
+        <v>4</v>
+      </c>
+      <c r="H824">
+        <v>4</v>
+      </c>
+      <c r="K824">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="825" spans="1:13">
+      <c r="A825">
+        <v>480743</v>
+      </c>
+      <c r="B825" t="s">
+        <v>491</v>
+      </c>
+      <c r="C825">
+        <v>2026</v>
+      </c>
+      <c r="D825" t="s">
+        <v>518</v>
+      </c>
+      <c r="E825">
+        <v>3</v>
+      </c>
+      <c r="H825">
+        <v>3</v>
+      </c>
+      <c r="K825">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="826" spans="1:13">
+      <c r="A826">
+        <v>88882</v>
+      </c>
+      <c r="B826" t="s">
+        <v>239</v>
+      </c>
+      <c r="C826">
+        <v>2026</v>
+      </c>
+      <c r="D826" t="s">
+        <v>518</v>
+      </c>
+      <c r="E826">
+        <v>4</v>
+      </c>
+      <c r="H826">
+        <v>4</v>
+      </c>
+      <c r="K826">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="827" spans="1:13">
+      <c r="A827">
+        <v>4663</v>
+      </c>
+      <c r="B827" t="s">
+        <v>238</v>
+      </c>
+      <c r="C827">
+        <v>2026</v>
+      </c>
+      <c r="D827" t="s">
+        <v>518</v>
+      </c>
+      <c r="E827">
+        <v>1</v>
+      </c>
+      <c r="H827">
+        <v>1</v>
+      </c>
+      <c r="K827">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="828" spans="1:13">
+      <c r="A828">
+        <v>70892</v>
+      </c>
+      <c r="B828" t="s">
+        <v>241</v>
+      </c>
+      <c r="C828">
+        <v>2026</v>
+      </c>
+      <c r="D828" t="s">
+        <v>518</v>
+      </c>
+      <c r="E828">
+        <v>4</v>
+      </c>
+      <c r="H828">
+        <v>4</v>
+      </c>
+      <c r="K828">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="829" spans="1:13">
+      <c r="A829">
+        <v>85555</v>
+      </c>
+      <c r="B829" t="s">
+        <v>247</v>
+      </c>
+      <c r="C829">
+        <v>2026</v>
+      </c>
+      <c r="D829" t="s">
+        <v>518</v>
+      </c>
+      <c r="E829">
+        <v>3</v>
+      </c>
+      <c r="H829">
+        <v>3</v>
+      </c>
+      <c r="K829">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="830" spans="1:13">
+      <c r="A830">
+        <v>104690</v>
+      </c>
+      <c r="B830" t="s">
+        <v>250</v>
+      </c>
+      <c r="C830">
+        <v>2026</v>
+      </c>
+      <c r="D830" t="s">
+        <v>518</v>
+      </c>
+      <c r="E830">
+        <v>3</v>
+      </c>
+      <c r="H830">
+        <v>3</v>
+      </c>
+      <c r="K830">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="831" spans="1:13">
+      <c r="A831">
+        <v>55958</v>
+      </c>
+      <c r="B831" t="s">
+        <v>254</v>
+      </c>
+      <c r="C831">
+        <v>2026</v>
+      </c>
+      <c r="D831" t="s">
+        <v>518</v>
+      </c>
+      <c r="E831">
+        <v>4</v>
+      </c>
+      <c r="H831">
+        <v>4</v>
+      </c>
+      <c r="K831">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="832" spans="1:13">
+      <c r="A832">
+        <v>89841</v>
+      </c>
+      <c r="B832" t="s">
+        <v>511</v>
+      </c>
+      <c r="C832">
+        <v>2026</v>
+      </c>
+      <c r="D832" t="s">
+        <v>520</v>
+      </c>
+      <c r="E832">
+        <v>5</v>
+      </c>
+      <c r="F832">
+        <v>80</v>
+      </c>
+      <c r="G832">
+        <v>76</v>
+      </c>
+      <c r="H832">
+        <v>5</v>
+      </c>
+      <c r="I832">
+        <v>40</v>
+      </c>
+      <c r="J832">
+        <v>42.6</v>
+      </c>
+      <c r="K832">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="833" spans="1:11">
+      <c r="A833">
+        <v>19359</v>
+      </c>
+      <c r="B833" t="s">
+        <v>259</v>
+      </c>
+      <c r="C833">
+        <v>2026</v>
+      </c>
+      <c r="D833" t="s">
+        <v>518</v>
+      </c>
+      <c r="E833">
+        <v>4</v>
+      </c>
+      <c r="H833">
+        <v>4</v>
+      </c>
+      <c r="K833">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="834" spans="1:11">
+      <c r="A834">
+        <v>129750</v>
+      </c>
+      <c r="B834" t="s">
+        <v>261</v>
+      </c>
+      <c r="C834">
+        <v>2026</v>
+      </c>
+      <c r="D834" t="s">
+        <v>518</v>
+      </c>
+      <c r="E834">
+        <v>2</v>
+      </c>
+      <c r="H834">
+        <v>2</v>
+      </c>
+      <c r="K834">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="835" spans="1:11">
+      <c r="A835">
+        <v>20571</v>
+      </c>
+      <c r="B835" t="s">
+        <v>264</v>
+      </c>
+      <c r="C835">
+        <v>2026</v>
+      </c>
+      <c r="D835" t="s">
+        <v>518</v>
+      </c>
+      <c r="E835">
+        <v>3</v>
+      </c>
+      <c r="H835">
+        <v>3</v>
+      </c>
+      <c r="K835">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="836" spans="1:11">
+      <c r="A836">
+        <v>482560</v>
+      </c>
+      <c r="B836" t="s">
+        <v>220</v>
+      </c>
+      <c r="C836">
+        <v>2026</v>
+      </c>
+      <c r="D836" t="s">
+        <v>518</v>
+      </c>
+      <c r="E836">
+        <v>2</v>
+      </c>
+      <c r="H836">
+        <v>2</v>
+      </c>
+      <c r="K836">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="837" spans="1:11">
+      <c r="A837">
+        <v>9205</v>
+      </c>
+      <c r="B837" t="s">
+        <v>424</v>
+      </c>
+      <c r="C837">
+        <v>2026</v>
+      </c>
+      <c r="D837" t="s">
+        <v>518</v>
+      </c>
+      <c r="E837">
+        <v>4</v>
+      </c>
+      <c r="H837">
+        <v>4</v>
+      </c>
+      <c r="K837">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="838" spans="1:11">
+      <c r="A838">
+        <v>4866</v>
+      </c>
+      <c r="B838" t="s">
+        <v>275</v>
+      </c>
+      <c r="C838">
+        <v>2026</v>
+      </c>
+      <c r="D838" t="s">
+        <v>518</v>
+      </c>
+      <c r="E838">
+        <v>3</v>
+      </c>
+      <c r="H838">
+        <v>3</v>
+      </c>
+      <c r="K838">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="839" spans="1:11">
+      <c r="A839">
+        <v>107179</v>
+      </c>
+      <c r="B839" t="s">
+        <v>281</v>
+      </c>
+      <c r="C839">
+        <v>2026</v>
+      </c>
+      <c r="D839" t="s">
+        <v>518</v>
+      </c>
+      <c r="E839">
+        <v>3</v>
+      </c>
+      <c r="H839">
+        <v>3</v>
+      </c>
+      <c r="K839">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="840" spans="1:11">
+      <c r="A840">
+        <v>478942</v>
+      </c>
+      <c r="B840" t="s">
+        <v>494</v>
+      </c>
+      <c r="C840">
+        <v>2026</v>
+      </c>
+      <c r="D840" t="s">
+        <v>518</v>
+      </c>
+      <c r="E840">
+        <v>3</v>
+      </c>
+      <c r="H840">
+        <v>3</v>
+      </c>
+      <c r="K840">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="841" spans="1:11">
+      <c r="A841">
+        <v>106930</v>
+      </c>
+      <c r="B841" t="s">
+        <v>300</v>
+      </c>
+      <c r="C841">
+        <v>2026</v>
+      </c>
+      <c r="D841" t="s">
+        <v>518</v>
+      </c>
+      <c r="E841">
+        <v>3</v>
+      </c>
+      <c r="H841">
+        <v>3</v>
+      </c>
+      <c r="K841">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="842" spans="1:11">
+      <c r="A842">
+        <v>65137</v>
+      </c>
+      <c r="B842" t="s">
+        <v>303</v>
+      </c>
+      <c r="C842">
+        <v>2026</v>
+      </c>
+      <c r="D842" t="s">
+        <v>520</v>
+      </c>
+      <c r="E842">
+        <v>7</v>
+      </c>
+      <c r="F842">
+        <v>58</v>
+      </c>
+      <c r="G842">
+        <v>53.71428571428572</v>
+      </c>
+      <c r="H842">
+        <v>7</v>
+      </c>
+      <c r="I842">
+        <v>43</v>
+      </c>
+      <c r="J842">
+        <v>46.57142857142857</v>
+      </c>
+      <c r="K842">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="843" spans="1:11">
+      <c r="A843">
+        <v>84864</v>
+      </c>
+      <c r="B843" t="s">
+        <v>305</v>
+      </c>
+      <c r="C843">
+        <v>2026</v>
+      </c>
+      <c r="D843" t="s">
+        <v>518</v>
+      </c>
+      <c r="E843">
+        <v>3</v>
+      </c>
+      <c r="H843">
+        <v>3</v>
+      </c>
+      <c r="K843">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="844" spans="1:11">
+      <c r="A844">
+        <v>85114</v>
+      </c>
+      <c r="B844" t="s">
+        <v>512</v>
+      </c>
+      <c r="C844">
+        <v>2026</v>
+      </c>
+      <c r="D844" t="s">
+        <v>518</v>
+      </c>
+      <c r="E844">
+        <v>4</v>
+      </c>
+      <c r="H844">
+        <v>4</v>
+      </c>
+      <c r="K844">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="845" spans="1:11">
+      <c r="A845">
+        <v>121754</v>
+      </c>
+      <c r="B845" t="s">
+        <v>306</v>
+      </c>
+      <c r="C845">
+        <v>2026</v>
+      </c>
+      <c r="D845" t="s">
+        <v>518</v>
+      </c>
+      <c r="E845">
+        <v>2</v>
+      </c>
+      <c r="H845">
+        <v>2</v>
+      </c>
+      <c r="K845">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="846" spans="1:11">
+      <c r="A846">
+        <v>40200</v>
+      </c>
+      <c r="B846" t="s">
+        <v>318</v>
+      </c>
+      <c r="C846">
+        <v>2026</v>
+      </c>
+      <c r="D846" t="s">
+        <v>518</v>
+      </c>
+      <c r="E846">
+        <v>4</v>
+      </c>
+      <c r="H846">
+        <v>4</v>
+      </c>
+      <c r="K846">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="847" spans="1:11">
+      <c r="A847">
+        <v>84202</v>
+      </c>
+      <c r="B847" t="s">
+        <v>513</v>
+      </c>
+      <c r="C847">
+        <v>2026</v>
+      </c>
+      <c r="D847" t="s">
+        <v>518</v>
+      </c>
+      <c r="E847">
+        <v>1</v>
+      </c>
+      <c r="H847">
+        <v>1</v>
+      </c>
+      <c r="K847">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="848" spans="1:11">
+      <c r="A848">
+        <v>263810</v>
+      </c>
+      <c r="B848" t="s">
+        <v>329</v>
+      </c>
+      <c r="C848">
+        <v>2026</v>
+      </c>
+      <c r="D848" t="s">
+        <v>518</v>
+      </c>
+      <c r="E848">
+        <v>1</v>
+      </c>
+      <c r="H848">
+        <v>1</v>
+      </c>
+      <c r="K848">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="849" spans="1:13">
+      <c r="A849">
+        <v>34229</v>
+      </c>
+      <c r="B849" t="s">
+        <v>21</v>
+      </c>
+      <c r="C849">
+        <v>2026</v>
+      </c>
+      <c r="D849" t="s">
+        <v>518</v>
+      </c>
+      <c r="E849">
+        <v>4</v>
+      </c>
+      <c r="H849">
+        <v>4</v>
+      </c>
+      <c r="K849">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="850" spans="1:13">
+      <c r="A850">
+        <v>52991</v>
+      </c>
+      <c r="B850" t="s">
+        <v>514</v>
+      </c>
+      <c r="C850">
+        <v>2026</v>
+      </c>
+      <c r="D850" t="s">
+        <v>519</v>
+      </c>
+      <c r="E850">
+        <v>4</v>
+      </c>
+      <c r="H850">
+        <v>4</v>
+      </c>
+      <c r="K850">
+        <v>8</v>
+      </c>
+      <c r="L850">
+        <v>97</v>
+      </c>
+      <c r="M850">
+        <v>96.75</v>
+      </c>
+    </row>
+    <row r="851" spans="1:13">
+      <c r="A851">
+        <v>264822</v>
+      </c>
+      <c r="B851" t="s">
+        <v>515</v>
+      </c>
+      <c r="C851">
+        <v>2026</v>
+      </c>
+      <c r="D851" t="s">
+        <v>518</v>
+      </c>
+      <c r="E851">
+        <v>4</v>
+      </c>
+      <c r="H851">
+        <v>4</v>
+      </c>
+      <c r="K851">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="852" spans="1:13">
+      <c r="A852">
+        <v>268015</v>
+      </c>
+      <c r="B852" t="s">
+        <v>48</v>
+      </c>
+      <c r="C852">
+        <v>2026</v>
+      </c>
+      <c r="D852" t="s">
+        <v>518</v>
+      </c>
+      <c r="E852">
+        <v>1</v>
+      </c>
+      <c r="H852">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="853" spans="1:13">
+      <c r="A853">
+        <v>133572</v>
+      </c>
+      <c r="B853" t="s">
+        <v>45</v>
+      </c>
+      <c r="C853">
+        <v>2026</v>
+      </c>
+      <c r="D853" t="s">
+        <v>518</v>
+      </c>
+      <c r="E853">
+        <v>1</v>
+      </c>
+      <c r="H853">
+        <v>1</v>
+      </c>
+      <c r="K853">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="854" spans="1:13">
+      <c r="A854">
+        <v>25033</v>
+      </c>
+      <c r="B854" t="s">
+        <v>18</v>
+      </c>
+      <c r="C854">
+        <v>2026</v>
+      </c>
+      <c r="D854" t="s">
+        <v>519</v>
+      </c>
+      <c r="E854">
+        <v>2</v>
+      </c>
+      <c r="H854">
+        <v>2</v>
+      </c>
+      <c r="K854">
+        <v>9</v>
+      </c>
+      <c r="L854">
+        <v>96</v>
+      </c>
+      <c r="M854">
+        <v>90.88888888888889</v>
+      </c>
+    </row>
+    <row r="855" spans="1:13">
+      <c r="A855">
+        <v>279315</v>
+      </c>
+      <c r="B855" t="s">
+        <v>467</v>
+      </c>
+      <c r="C855">
+        <v>2026</v>
+      </c>
+      <c r="D855" t="s">
+        <v>520</v>
+      </c>
+      <c r="E855">
+        <v>5</v>
+      </c>
+      <c r="F855">
+        <v>33</v>
+      </c>
+      <c r="G855">
+        <v>34.2</v>
+      </c>
+      <c r="H855">
+        <v>5</v>
+      </c>
+      <c r="I855">
+        <v>20</v>
+      </c>
+      <c r="J855">
+        <v>17.8</v>
+      </c>
+      <c r="K855">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="856" spans="1:13">
+      <c r="A856">
+        <v>125191</v>
+      </c>
+      <c r="B856" t="s">
+        <v>428</v>
+      </c>
+      <c r="C856">
+        <v>2026</v>
+      </c>
+      <c r="D856" t="s">
+        <v>518</v>
+      </c>
+      <c r="E856">
+        <v>3</v>
+      </c>
+      <c r="H856">
+        <v>3</v>
+      </c>
+      <c r="K856">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="857" spans="1:13">
+      <c r="A857">
+        <v>264203</v>
+      </c>
+      <c r="B857" t="s">
+        <v>468</v>
+      </c>
+      <c r="C857">
+        <v>2026</v>
+      </c>
+      <c r="D857" t="s">
+        <v>518</v>
+      </c>
+      <c r="E857">
+        <v>2</v>
+      </c>
+      <c r="H857">
+        <v>2</v>
+      </c>
+      <c r="K857">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="858" spans="1:13">
+      <c r="A858">
+        <v>31707</v>
+      </c>
+      <c r="B858" t="s">
+        <v>20</v>
+      </c>
+      <c r="C858">
+        <v>2026</v>
+      </c>
+      <c r="D858" t="s">
+        <v>518</v>
+      </c>
+      <c r="E858">
+        <v>1</v>
+      </c>
+      <c r="H858">
+        <v>1</v>
+      </c>
+      <c r="K858">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="859" spans="1:13">
+      <c r="A859">
+        <v>482616</v>
+      </c>
+      <c r="B859" t="s">
+        <v>516</v>
+      </c>
+      <c r="C859">
+        <v>2026</v>
+      </c>
+      <c r="D859" t="s">
+        <v>518</v>
+      </c>
+      <c r="E859">
+        <v>4</v>
+      </c>
+      <c r="H859">
+        <v>4</v>
+      </c>
+      <c r="K859">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="860" spans="1:13">
+      <c r="A860">
+        <v>29950</v>
+      </c>
+      <c r="B860" t="s">
+        <v>19</v>
+      </c>
+      <c r="C860">
+        <v>2026</v>
+      </c>
+      <c r="D860" t="s">
+        <v>518</v>
+      </c>
+      <c r="E860">
+        <v>3</v>
+      </c>
+      <c r="H860">
+        <v>3</v>
+      </c>
+      <c r="K860">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="861" spans="1:13">
+      <c r="A861">
+        <v>114664</v>
+      </c>
+      <c r="B861" t="s">
+        <v>35</v>
+      </c>
+      <c r="C861">
+        <v>2026</v>
+      </c>
+      <c r="D861" t="s">
+        <v>519</v>
+      </c>
+      <c r="E861">
+        <v>4</v>
+      </c>
+      <c r="H861">
+        <v>4</v>
+      </c>
+      <c r="K861">
+        <v>12</v>
+      </c>
+      <c r="L861">
+        <v>87</v>
+      </c>
+      <c r="M861">
+        <v>77.66666666666667</v>
+      </c>
+    </row>
+    <row r="862" spans="1:13">
+      <c r="A862">
+        <v>478731</v>
+      </c>
+      <c r="B862" t="s">
+        <v>470</v>
+      </c>
+      <c r="C862">
+        <v>2026</v>
+      </c>
+      <c r="D862" t="s">
+        <v>518</v>
+      </c>
+      <c r="E862">
+        <v>4</v>
+      </c>
+      <c r="H862">
+        <v>4</v>
+      </c>
+      <c r="K862">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="863" spans="1:13">
+      <c r="A863">
+        <v>480997</v>
+      </c>
+      <c r="B863" t="s">
+        <v>517</v>
+      </c>
+      <c r="C863">
+        <v>2026</v>
+      </c>
+      <c r="D863" t="s">
+        <v>518</v>
+      </c>
+      <c r="E863">
+        <v>1</v>
+      </c>
+      <c r="H863">
+        <v>1</v>
+      </c>
+      <c r="K863">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="864" spans="1:13">
+      <c r="A864">
+        <v>131373</v>
+      </c>
+      <c r="B864" t="s">
+        <v>471</v>
+      </c>
+      <c r="C864">
+        <v>2026</v>
+      </c>
+      <c r="D864" t="s">
+        <v>518</v>
+      </c>
+      <c r="E864">
+        <v>4</v>
+      </c>
+      <c r="H864">
+        <v>4</v>
+      </c>
+      <c r="K864">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="865" spans="1:11">
+      <c r="A865">
+        <v>89967</v>
+      </c>
+      <c r="B865" t="s">
+        <v>345</v>
+      </c>
+      <c r="C865">
+        <v>2026</v>
+      </c>
+      <c r="D865" t="s">
+        <v>518</v>
+      </c>
+      <c r="E865">
+        <v>3</v>
+      </c>
+      <c r="H865">
+        <v>3</v>
+      </c>
+      <c r="K865">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="866" spans="1:11">
+      <c r="A866">
+        <v>484328</v>
+      </c>
+      <c r="B866" t="s">
+        <v>349</v>
+      </c>
+      <c r="C866">
+        <v>2026</v>
+      </c>
+      <c r="D866" t="s">
+        <v>518</v>
+      </c>
+      <c r="E866">
+        <v>3</v>
+      </c>
+      <c r="H866">
+        <v>3</v>
+      </c>
+      <c r="K866">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="867" spans="1:11">
+      <c r="A867">
+        <v>29894</v>
+      </c>
+      <c r="B867" t="s">
+        <v>473</v>
+      </c>
+      <c r="C867">
+        <v>2026</v>
+      </c>
+      <c r="D867" t="s">
+        <v>518</v>
+      </c>
+      <c r="E867">
+        <v>2</v>
+      </c>
+      <c r="H867">
+        <v>2</v>
+      </c>
+      <c r="K867">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="868" spans="1:11">
+      <c r="A868">
+        <v>75718</v>
+      </c>
+      <c r="B868" t="s">
+        <v>361</v>
+      </c>
+      <c r="C868">
+        <v>2026</v>
+      </c>
+      <c r="D868" t="s">
+        <v>518</v>
+      </c>
+      <c r="E868">
+        <v>4</v>
+      </c>
+      <c r="H868">
+        <v>4</v>
+      </c>
+      <c r="K868">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="869" spans="1:11">
+      <c r="A869">
+        <v>126772</v>
+      </c>
+      <c r="B869" t="s">
+        <v>372</v>
+      </c>
+      <c r="C869">
+        <v>2026</v>
+      </c>
+      <c r="D869" t="s">
+        <v>520</v>
+      </c>
+      <c r="E869">
+        <v>5</v>
+      </c>
+      <c r="F869">
+        <v>7</v>
+      </c>
+      <c r="G869">
+        <v>10.8</v>
+      </c>
+      <c r="H869">
+        <v>5</v>
+      </c>
+      <c r="I869">
+        <v>10</v>
+      </c>
+      <c r="J869">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K869">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="870" spans="1:11">
+      <c r="A870">
+        <v>82557</v>
+      </c>
+      <c r="B870" t="s">
+        <v>475</v>
+      </c>
+      <c r="C870">
+        <v>2026</v>
+      </c>
+      <c r="D870" t="s">
+        <v>518</v>
+      </c>
+      <c r="E870">
+        <v>4</v>
+      </c>
+      <c r="H870">
+        <v>4</v>
+      </c>
+      <c r="K870">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="871" spans="1:11">
+      <c r="A871">
+        <v>111213</v>
+      </c>
+      <c r="B871" t="s">
+        <v>387</v>
+      </c>
+      <c r="C871">
+        <v>2026</v>
+      </c>
+      <c r="D871" t="s">
+        <v>518</v>
+      </c>
+      <c r="E871">
+        <v>4</v>
+      </c>
+      <c r="H871">
+        <v>4</v>
+      </c>
+      <c r="K871">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="872" spans="1:11">
+      <c r="A872">
+        <v>111216</v>
+      </c>
+      <c r="B872" t="s">
+        <v>502</v>
+      </c>
+      <c r="C872">
+        <v>2026</v>
+      </c>
+      <c r="D872" t="s">
+        <v>518</v>
+      </c>
+      <c r="E872">
+        <v>3</v>
+      </c>
+      <c r="H872">
+        <v>3</v>
+      </c>
+      <c r="K872">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="873" spans="1:11">
+      <c r="A873">
+        <v>124924</v>
+      </c>
+      <c r="B873" t="s">
+        <v>432</v>
+      </c>
+      <c r="C873">
+        <v>2026</v>
+      </c>
+      <c r="D873" t="s">
+        <v>518</v>
+      </c>
+      <c r="E873">
+        <v>2</v>
+      </c>
+      <c r="H873">
+        <v>2</v>
+      </c>
+      <c r="K873">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
